--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -76,7 +76,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -114,7 +114,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -152,7 +152,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -190,7 +190,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -228,7 +228,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -10172,7 +10172,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId13"/>
 </worksheet>
@@ -10188,7 +10188,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId14"/>
 </worksheet>
@@ -10204,7 +10204,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId15"/>
 </worksheet>
@@ -10220,7 +10220,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId16"/>
 </worksheet>
@@ -10236,7 +10236,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId17"/>
 </worksheet>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -4,11 +4,6 @@
   <workbookPr date1904="false"/>
   <sheets>
     <sheet sheetId="1" name="Work Items" r:id="rId1"/>
-    <sheet sheetId="2" name="Aging Wip" r:id="rId2"/>
-    <sheet sheetId="3" name="Cfd Plot" r:id="rId3"/>
-    <sheet sheetId="4" name="Cycle Time Scatter" r:id="rId4"/>
-    <sheet sheetId="5" name="Forecasted Cfd Plot" r:id="rId5"/>
-    <sheet sheetId="6" name="Throughput Histogram" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -67,196 +62,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
   <sheetPr>
@@ -10160,84 +9965,4 @@
   <pageSetup/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId13"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId14"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId15"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId16"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId17"/>
-</worksheet>
 </file>
--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -4,6 +4,11 @@
   <workbookPr date1904="false"/>
   <sheets>
     <sheet sheetId="1" name="Work Items" r:id="rId1"/>
+    <sheet sheetId="2" name="Aging Wip" r:id="rId2"/>
+    <sheet sheetId="3" name="Cfd Plot" r:id="rId3"/>
+    <sheet sheetId="4" name="Cycle Time Scatter" r:id="rId4"/>
+    <sheet sheetId="5" name="Forecasted Cfd Plot" r:id="rId5"/>
+    <sheet sheetId="6" name="Throughput Histogram" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -62,6 +67,196 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
   <sheetPr>
@@ -9965,4 +10160,84 @@
   <pageSetup/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId13"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId14"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId15"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId16"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId17"/>
+</worksheet>
 </file>
--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -6,9 +6,10 @@
     <sheet sheetId="1" name="Work Items" r:id="rId1"/>
     <sheet sheetId="2" name="Aging Wip" r:id="rId2"/>
     <sheet sheetId="3" name="Cfd Plot" r:id="rId3"/>
-    <sheet sheetId="4" name="Cycle Time Scatter" r:id="rId4"/>
-    <sheet sheetId="5" name="Forecasted Cfd Plot" r:id="rId5"/>
-    <sheet sheetId="6" name="Throughput Histogram" r:id="rId6"/>
+    <sheet sheetId="4" name="Cycle Time Bands" r:id="rId4"/>
+    <sheet sheetId="5" name="Cycle Time Scatter" r:id="rId5"/>
+    <sheet sheetId="6" name="Forecasted Cfd Plot" r:id="rId6"/>
+    <sheet sheetId="7" name="Throughput Histogram" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -76,7 +77,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -85,7 +86,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -114,7 +115,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -123,7 +124,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -152,7 +153,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -161,7 +162,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -190,7 +191,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -199,7 +200,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -228,7 +229,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -237,7 +238,45 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5038725" cy="4667250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -262,7 +301,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N201"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="12.100000000000001" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -272,13 +311,16 @@
     <col width="14.3" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="14.3" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="15.400000000000002" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="22.0" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="16.5" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="17.6" min="11" max="11" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="12" max="12" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="13" max="13" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
+    <col width="13.200000000000001" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="11.0" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="7.700000000000001" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="22.0" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="12" max="12" bestFit="1" customWidth="1"/>
+    <col width="16.5" min="13" max="13" bestFit="1" customWidth="1"/>
+    <col width="17.6" min="14" max="14" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="16" max="16" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="17" max="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -319,35 +361,50 @@
       </c>
       <c r="H1" s="0" t="inlineStr">
         <is>
+          <t>YYYY-Week</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>YYYY-MM</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>YYYY</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
           <t>Cycle Time (days)</t>
         </is>
       </c>
-      <c r="I1" s="0" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>Current Age (days)</t>
         </is>
       </c>
-      <c r="J1" s="0" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 1 day</t>
         </is>
       </c>
-      <c r="K1" s="0" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 7 days</t>
         </is>
       </c>
-      <c r="L1" s="0" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 14 days</t>
         </is>
       </c>
-      <c r="M1" s="0" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 21 days</t>
         </is>
       </c>
-      <c r="N1" s="0" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 28 days</t>
         </is>
@@ -385,23 +442,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>2025-W42</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K2" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I2" s="0"/>
-      <c r="J2" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L2" s="0"/>
       <c r="M2" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -437,23 +507,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>2025-W43</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="I3" s="0"/>
-      <c r="J3" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L3" s="0"/>
       <c r="M3" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -489,23 +572,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>2025-W44</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I4" s="0"/>
-      <c r="J4" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L4" s="0"/>
       <c r="M4" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -541,23 +637,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>2025-W45</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I5" s="0"/>
-      <c r="J5" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L5" s="0"/>
       <c r="M5" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -593,23 +702,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>2025-W44</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="I6" s="0"/>
-      <c r="J6" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L6" s="0"/>
       <c r="M6" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -645,23 +767,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>2025-W44</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="I7" s="0"/>
-      <c r="J7" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L7" s="0"/>
       <c r="M7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -697,23 +832,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>2025-W44</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I8" s="0"/>
-      <c r="J8" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L8" s="0"/>
       <c r="M8" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -749,23 +897,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>2025-W44</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I9" s="0"/>
-      <c r="J9" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L9" s="0"/>
       <c r="M9" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -801,23 +962,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>2025-W44</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K10" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="I10" s="0"/>
-      <c r="J10" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L10" s="0"/>
       <c r="M10" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -853,23 +1027,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>2025-W46</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K11" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="I11" s="0"/>
-      <c r="J11" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L11" s="0"/>
       <c r="M11" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -905,23 +1092,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>2025-W46</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="I12" s="0"/>
-      <c r="J12" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L12" s="0"/>
       <c r="M12" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -957,23 +1157,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>2025-W44</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K13" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="0"/>
-      <c r="J13" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L13" s="0"/>
       <c r="M13" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1009,23 +1222,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>2025-W46</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K14" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="I14" s="0"/>
-      <c r="J14" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L14" s="0"/>
       <c r="M14" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1061,23 +1287,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>2025-W44</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K15" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I15" s="0"/>
-      <c r="J15" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L15" s="0"/>
       <c r="M15" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1113,23 +1352,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>2025-W47</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K16" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="I16" s="0"/>
-      <c r="J16" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L16" s="0"/>
       <c r="M16" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1165,23 +1417,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>2025-W47</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K17" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I17" s="0"/>
-      <c r="J17" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L17" s="0"/>
       <c r="M17" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1217,23 +1482,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H18" s="0" t="n">
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>2025-W46</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K18" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="I18" s="0"/>
-      <c r="J18" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L18" s="0"/>
       <c r="M18" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1269,23 +1547,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>2025-W46</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K19" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="I19" s="0"/>
-      <c r="J19" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L19" s="0"/>
       <c r="M19" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1321,23 +1612,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H20" s="0" t="n">
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>2025-W46</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K20" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I20" s="0"/>
-      <c r="J20" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L20" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L20" s="0"/>
       <c r="M20" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1373,23 +1677,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>2025-W46</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K21" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I21" s="0"/>
-      <c r="J21" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L21" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L21" s="0"/>
       <c r="M21" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1425,23 +1742,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H22" s="0" t="n">
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>2025-W48</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K22" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="I22" s="0"/>
-      <c r="J22" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L22" s="0"/>
       <c r="M22" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1477,23 +1807,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H23" s="0" t="n">
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>2025-W46</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K23" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="0"/>
-      <c r="J23" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L23" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L23" s="0"/>
       <c r="M23" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1529,23 +1872,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>2025-W49</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K24" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="I24" s="0"/>
-      <c r="J24" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L24" s="0"/>
       <c r="M24" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1581,23 +1937,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>2025-W48</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K25" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="I25" s="0"/>
-      <c r="J25" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L25" s="0"/>
       <c r="M25" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1633,23 +2002,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H26" s="0" t="n">
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>2025-W48</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K26" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="I26" s="0"/>
-      <c r="J26" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L26" s="0"/>
       <c r="M26" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P26" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1685,23 +2067,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>2025-W48</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K27" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="I27" s="0"/>
-      <c r="J27" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L27" s="0"/>
       <c r="M27" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1737,23 +2132,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>2025-W47</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K28" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I28" s="0"/>
-      <c r="J28" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L28" s="0"/>
       <c r="M28" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1789,23 +2197,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H29" s="0" t="n">
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>2025-W47</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K29" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I29" s="0"/>
-      <c r="J29" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L29" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L29" s="0"/>
       <c r="M29" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1841,23 +2262,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H30" s="0" t="n">
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>2025-W47</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K30" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I30" s="0"/>
-      <c r="J30" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L30" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L30" s="0"/>
       <c r="M30" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1893,23 +2327,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H31" s="0" t="n">
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>2025-W47</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K31" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="I31" s="0"/>
-      <c r="J31" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L31" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L31" s="0"/>
       <c r="M31" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1945,23 +2392,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H32" s="0" t="n">
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>2025-W48</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K32" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="I32" s="0"/>
-      <c r="J32" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L32" s="0"/>
       <c r="M32" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P32" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1997,23 +2457,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H33" s="0" t="n">
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t>2025-W48</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K33" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I33" s="0"/>
-      <c r="J33" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L33" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L33" s="0"/>
       <c r="M33" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O33" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P33" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2049,23 +2522,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H34" s="0" t="n">
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t>2025-W49</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K34" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="I34" s="0"/>
-      <c r="J34" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K34" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L34" s="0"/>
       <c r="M34" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P34" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2101,23 +2587,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H35" s="0" t="n">
+      <c r="H35" s="0" t="inlineStr">
+        <is>
+          <t>2025-W48</t>
+        </is>
+      </c>
+      <c r="I35" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K35" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="I35" s="0"/>
-      <c r="J35" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L35" s="0"/>
       <c r="M35" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P35" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2153,23 +2652,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H36" s="0" t="n">
+      <c r="H36" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I36" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K36" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="I36" s="0"/>
-      <c r="J36" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K36" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L36" s="0"/>
       <c r="M36" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O36" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2205,23 +2717,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H37" s="0" t="n">
+      <c r="H37" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K37" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="I37" s="0"/>
-      <c r="J37" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L37" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L37" s="0"/>
       <c r="M37" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O37" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2257,23 +2782,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H38" s="0" t="n">
+      <c r="H38" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I38" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J38" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K38" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="I38" s="0"/>
-      <c r="J38" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K38" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L38" s="0"/>
       <c r="M38" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O38" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2309,23 +2847,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H39" s="0" t="n">
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>2025-W48</t>
+        </is>
+      </c>
+      <c r="I39" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K39" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I39" s="0"/>
-      <c r="J39" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L39" s="0"/>
       <c r="M39" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O39" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2361,23 +2912,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H40" s="0" t="n">
+      <c r="H40" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I40" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J40" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K40" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I40" s="0"/>
-      <c r="J40" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K40" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L40" s="0"/>
       <c r="M40" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2413,23 +2977,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H41" s="0" t="n">
+      <c r="H41" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I41" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J41" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K41" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I41" s="0"/>
-      <c r="J41" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K41" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L41" s="0"/>
       <c r="M41" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O41" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2465,23 +3042,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H42" s="0" t="n">
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t>2025-W48</t>
+        </is>
+      </c>
+      <c r="I42" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J42" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K42" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="I42" s="0"/>
-      <c r="J42" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K42" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L42" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L42" s="0"/>
       <c r="M42" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P42" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2517,23 +3107,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H43" s="0" t="n">
+      <c r="H43" s="0" t="inlineStr">
+        <is>
+          <t>2025-W51</t>
+        </is>
+      </c>
+      <c r="I43" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J43" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K43" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I43" s="0"/>
-      <c r="J43" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L43" s="0"/>
       <c r="M43" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O43" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2569,23 +3172,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H44" s="0" t="n">
+      <c r="H44" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I44" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K44" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I44" s="0"/>
-      <c r="J44" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K44" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L44" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L44" s="0"/>
       <c r="M44" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O44" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P44" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2621,23 +3237,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H45" s="0" t="n">
+      <c r="H45" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I45" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J45" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K45" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I45" s="0"/>
-      <c r="J45" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K45" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L45" s="0"/>
       <c r="M45" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O45" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P45" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2673,23 +3302,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H46" s="0" t="n">
+      <c r="H46" s="0" t="inlineStr">
+        <is>
+          <t>2025-W49</t>
+        </is>
+      </c>
+      <c r="I46" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J46" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K46" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="I46" s="0"/>
-      <c r="J46" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K46" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L46" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L46" s="0"/>
       <c r="M46" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O46" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P46" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2725,23 +3367,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H47" s="0" t="n">
+      <c r="H47" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I47" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K47" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I47" s="0"/>
-      <c r="J47" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K47" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L47" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L47" s="0"/>
       <c r="M47" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O47" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P47" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2777,23 +3432,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H48" s="0" t="n">
+      <c r="H48" s="0" t="inlineStr">
+        <is>
+          <t>2025-W52</t>
+        </is>
+      </c>
+      <c r="I48" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K48" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="I48" s="0"/>
-      <c r="J48" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L48" s="0"/>
       <c r="M48" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O48" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2829,23 +3497,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H49" s="0" t="n">
+      <c r="H49" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I49" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J49" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K49" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="I49" s="0"/>
-      <c r="J49" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L49" s="0"/>
       <c r="M49" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O49" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P49" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2881,23 +3562,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H50" s="0" t="n">
+      <c r="H50" s="0" t="inlineStr">
+        <is>
+          <t>2025-W51</t>
+        </is>
+      </c>
+      <c r="I50" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J50" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K50" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I50" s="0"/>
-      <c r="J50" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L50" s="0"/>
       <c r="M50" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O50" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2933,23 +3627,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H51" s="0" t="n">
+      <c r="H51" s="0" t="inlineStr">
+        <is>
+          <t>2025-W52</t>
+        </is>
+      </c>
+      <c r="I51" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J51" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K51" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="I51" s="0"/>
-      <c r="J51" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L51" s="0"/>
       <c r="M51" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O51" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2985,23 +3692,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H52" s="0" t="n">
+      <c r="H52" s="0" t="inlineStr">
+        <is>
+          <t>2025-W51</t>
+        </is>
+      </c>
+      <c r="I52" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J52" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K52" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I52" s="0"/>
-      <c r="J52" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L52" s="0"/>
       <c r="M52" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O52" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3037,23 +3757,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H53" s="0" t="n">
+      <c r="H53" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I53" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J53" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K53" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I53" s="0"/>
-      <c r="J53" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L53" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L53" s="0"/>
       <c r="M53" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O53" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P53" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3089,23 +3822,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H54" s="0" t="n">
+      <c r="H54" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I54" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J54" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K54" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I54" s="0"/>
-      <c r="J54" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L54" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L54" s="0"/>
       <c r="M54" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O54" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P54" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3141,23 +3887,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H55" s="0" t="n">
+      <c r="H55" s="0" t="inlineStr">
+        <is>
+          <t>2025-W52</t>
+        </is>
+      </c>
+      <c r="I55" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J55" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K55" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I55" s="0"/>
-      <c r="J55" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K55" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L55" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L55" s="0"/>
       <c r="M55" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O55" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3193,23 +3952,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H56" s="0" t="n">
+      <c r="H56" s="0" t="inlineStr">
+        <is>
+          <t>2025-W52</t>
+        </is>
+      </c>
+      <c r="I56" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J56" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K56" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="I56" s="0"/>
-      <c r="J56" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K56" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L56" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L56" s="0"/>
       <c r="M56" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O56" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3245,23 +4017,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H57" s="0" t="n">
+      <c r="H57" s="0" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="I57" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J57" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K57" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="I57" s="0"/>
-      <c r="J57" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K57" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L57" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L57" s="0"/>
       <c r="M57" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O57" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3297,23 +4082,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H58" s="0" t="n">
+      <c r="H58" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I58" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J58" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K58" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="0"/>
-      <c r="J58" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L58" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L58" s="0"/>
       <c r="M58" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O58" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P58" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3349,23 +4147,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H59" s="0" t="n">
+      <c r="H59" s="0" t="inlineStr">
+        <is>
+          <t>2025-W52</t>
+        </is>
+      </c>
+      <c r="I59" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J59" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K59" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="I59" s="0"/>
-      <c r="J59" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L59" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L59" s="0"/>
       <c r="M59" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O59" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P59" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3401,23 +4212,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H60" s="0" t="n">
+      <c r="H60" s="0" t="inlineStr">
+        <is>
+          <t>2025-W51</t>
+        </is>
+      </c>
+      <c r="I60" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J60" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K60" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I60" s="0"/>
-      <c r="J60" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L60" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L60" s="0"/>
       <c r="M60" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O60" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P60" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3453,23 +4277,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H61" s="0" t="n">
+      <c r="H61" s="0" t="inlineStr">
+        <is>
+          <t>2025-W52</t>
+        </is>
+      </c>
+      <c r="I61" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J61" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K61" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="I61" s="0"/>
-      <c r="J61" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L61" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L61" s="0"/>
       <c r="M61" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O61" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P61" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3505,23 +4342,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H62" s="0" t="n">
+      <c r="H62" s="0" t="inlineStr">
+        <is>
+          <t>2025-W52</t>
+        </is>
+      </c>
+      <c r="I62" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J62" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K62" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I62" s="0"/>
-      <c r="J62" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L62" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L62" s="0"/>
       <c r="M62" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O62" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P62" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3557,23 +4407,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H63" s="0" t="n">
+      <c r="H63" s="0" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="I63" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J63" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K63" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="I63" s="0"/>
-      <c r="J63" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L63" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L63" s="0"/>
       <c r="M63" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O63" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3609,23 +4472,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H64" s="0" t="n">
+      <c r="H64" s="0" t="inlineStr">
+        <is>
+          <t>2025-W51</t>
+        </is>
+      </c>
+      <c r="I64" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J64" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K64" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I64" s="0"/>
-      <c r="J64" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K64" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L64" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L64" s="0"/>
       <c r="M64" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O64" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P64" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3661,23 +4537,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H65" s="0" t="n">
+      <c r="H65" s="0" t="inlineStr">
+        <is>
+          <t>2025-W52</t>
+        </is>
+      </c>
+      <c r="I65" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J65" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K65" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="I65" s="0"/>
-      <c r="J65" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K65" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L65" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L65" s="0"/>
       <c r="M65" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O65" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P65" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3713,23 +4602,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H66" s="0" t="n">
+      <c r="H66" s="0" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="I66" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J66" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K66" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="I66" s="0"/>
-      <c r="J66" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L66" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L66" s="0"/>
       <c r="M66" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N66" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P66" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3765,23 +4667,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H67" s="0" t="n">
+      <c r="H67" s="0" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="I67" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J67" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K67" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I67" s="0"/>
-      <c r="J67" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K67" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L67" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L67" s="0"/>
       <c r="M67" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N67" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O67" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3817,23 +4732,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H68" s="0" t="n">
+      <c r="H68" s="0" t="inlineStr">
+        <is>
+          <t>2025-W52</t>
+        </is>
+      </c>
+      <c r="I68" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J68" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K68" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I68" s="0"/>
-      <c r="J68" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K68" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L68" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L68" s="0"/>
       <c r="M68" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N68" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O68" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P68" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3869,23 +4797,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H69" s="0" t="n">
+      <c r="H69" s="0" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="I69" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J69" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K69" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="I69" s="0"/>
-      <c r="J69" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K69" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L69" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L69" s="0"/>
       <c r="M69" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N69" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O69" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3921,23 +4862,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H70" s="0" t="n">
+      <c r="H70" s="0" t="inlineStr">
+        <is>
+          <t>2025-W52</t>
+        </is>
+      </c>
+      <c r="I70" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J70" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K70" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I70" s="0"/>
-      <c r="J70" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L70" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L70" s="0"/>
       <c r="M70" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N70" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O70" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P70" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3973,23 +4927,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H71" s="0" t="n">
+      <c r="H71" s="0" t="inlineStr">
+        <is>
+          <t>2025-W51</t>
+        </is>
+      </c>
+      <c r="I71" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J71" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K71" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="I71" s="0"/>
-      <c r="J71" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K71" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L71" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L71" s="0"/>
       <c r="M71" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N71" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O71" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P71" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4025,23 +4992,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H72" s="0" t="n">
+      <c r="H72" s="0" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="I72" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J72" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K72" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="I72" s="0"/>
-      <c r="J72" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K72" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L72" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L72" s="0"/>
       <c r="M72" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N72" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O72" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P72" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4077,23 +5057,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H73" s="0" t="n">
+      <c r="H73" s="0" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="I73" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J73" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K73" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="I73" s="0"/>
-      <c r="J73" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K73" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L73" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L73" s="0"/>
       <c r="M73" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N73" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O73" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P73" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4129,23 +5122,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H74" s="0" t="n">
+      <c r="H74" s="0" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="I74" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J74" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K74" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="I74" s="0"/>
-      <c r="J74" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K74" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L74" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L74" s="0"/>
       <c r="M74" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N74" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O74" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P74" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4181,23 +5187,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H75" s="0" t="n">
+      <c r="H75" s="0" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="I75" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J75" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K75" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="I75" s="0"/>
-      <c r="J75" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L75" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L75" s="0"/>
       <c r="M75" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N75" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O75" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P75" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4233,23 +5252,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H76" s="0" t="n">
+      <c r="H76" s="0" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="I76" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J76" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K76" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="I76" s="0"/>
-      <c r="J76" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L76" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L76" s="0"/>
       <c r="M76" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O76" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P76" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q76" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4285,23 +5317,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H77" s="0" t="n">
+      <c r="H77" s="0" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="I77" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J77" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K77" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I77" s="0"/>
-      <c r="J77" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L77" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L77" s="0"/>
       <c r="M77" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N77" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O77" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P77" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4337,23 +5382,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H78" s="0" t="n">
+      <c r="H78" s="0" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="I78" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J78" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K78" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I78" s="0"/>
-      <c r="J78" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L78" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L78" s="0"/>
       <c r="M78" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N78" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O78" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P78" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q78" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4389,23 +5447,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H79" s="0" t="n">
+      <c r="H79" s="0" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="I79" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J79" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K79" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I79" s="0"/>
-      <c r="J79" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L79" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L79" s="0"/>
       <c r="M79" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N79" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O79" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P79" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q79" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4441,23 +5512,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H80" s="0" t="n">
+      <c r="H80" s="0" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="I80" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J80" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K80" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="I80" s="0"/>
-      <c r="J80" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L80" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L80" s="0"/>
       <c r="M80" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N80" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O80" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P80" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q80" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4493,23 +5577,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H81" s="0" t="n">
+      <c r="H81" s="0" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="I81" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J81" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K81" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="I81" s="0"/>
-      <c r="J81" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L81" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L81" s="0"/>
       <c r="M81" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N81" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O81" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P81" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q81" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4545,23 +5642,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H82" s="0" t="n">
+      <c r="H82" s="0" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="I82" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J82" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K82" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="I82" s="0"/>
-      <c r="J82" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K82" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L82" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L82" s="0"/>
       <c r="M82" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O82" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P82" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q82" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4597,23 +5707,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H83" s="0" t="n">
+      <c r="H83" s="0" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="I83" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J83" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K83" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="I83" s="0"/>
-      <c r="J83" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K83" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L83" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L83" s="0"/>
       <c r="M83" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N83" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O83" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P83" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q83" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4649,23 +5772,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H84" s="0" t="n">
+      <c r="H84" s="0" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="I84" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J84" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K84" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="I84" s="0"/>
-      <c r="J84" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L84" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L84" s="0"/>
       <c r="M84" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O84" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P84" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q84" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4701,23 +5837,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H85" s="0" t="n">
+      <c r="H85" s="0" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="I85" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J85" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K85" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="I85" s="0"/>
-      <c r="J85" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K85" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L85" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L85" s="0"/>
       <c r="M85" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O85" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P85" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q85" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4753,23 +5902,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H86" s="0" t="n">
+      <c r="H86" s="0" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="I86" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J86" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K86" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="I86" s="0"/>
-      <c r="J86" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K86" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L86" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L86" s="0"/>
       <c r="M86" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N86" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O86" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P86" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q86" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4805,23 +5967,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H87" s="0" t="n">
+      <c r="H87" s="0" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="I87" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J87" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K87" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="I87" s="0"/>
-      <c r="J87" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K87" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L87" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L87" s="0"/>
       <c r="M87" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N87" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O87" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P87" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q87" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4857,23 +6032,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H88" s="0" t="n">
+      <c r="H88" s="0" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="I88" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J88" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K88" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I88" s="0"/>
-      <c r="J88" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K88" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L88" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L88" s="0"/>
       <c r="M88" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N88" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O88" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P88" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q88" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4909,23 +6097,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H89" s="0" t="n">
+      <c r="H89" s="0" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="I89" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J89" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K89" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I89" s="0"/>
-      <c r="J89" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K89" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L89" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L89" s="0"/>
       <c r="M89" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N89" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O89" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P89" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q89" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4961,23 +6162,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H90" s="0" t="n">
+      <c r="H90" s="0" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="I90" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J90" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K90" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I90" s="0"/>
-      <c r="J90" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K90" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L90" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L90" s="0"/>
       <c r="M90" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N90" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O90" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P90" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q90" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5013,23 +6227,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H91" s="0" t="n">
+      <c r="H91" s="0" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="I91" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J91" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K91" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I91" s="0"/>
-      <c r="J91" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K91" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L91" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L91" s="0"/>
       <c r="M91" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N91" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O91" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P91" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q91" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5065,23 +6292,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H92" s="0" t="n">
+      <c r="H92" s="0" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="I92" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J92" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K92" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I92" s="0"/>
-      <c r="J92" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K92" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L92" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L92" s="0"/>
       <c r="M92" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N92" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O92" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P92" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q92" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5117,23 +6357,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H93" s="0" t="n">
+      <c r="H93" s="0" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="I93" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J93" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K93" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I93" s="0"/>
-      <c r="J93" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K93" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L93" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L93" s="0"/>
       <c r="M93" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N93" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O93" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P93" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q93" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5169,23 +6422,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H94" s="0" t="n">
+      <c r="H94" s="0" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="I94" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J94" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K94" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="I94" s="0"/>
-      <c r="J94" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K94" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L94" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L94" s="0"/>
       <c r="M94" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N94" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O94" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P94" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q94" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5221,23 +6487,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H95" s="0" t="n">
+      <c r="H95" s="0" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="I95" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J95" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K95" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I95" s="0"/>
-      <c r="J95" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K95" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L95" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L95" s="0"/>
       <c r="M95" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N95" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O95" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P95" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q95" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5273,23 +6552,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H96" s="0" t="n">
+      <c r="H96" s="0" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="I96" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J96" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K96" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="I96" s="0"/>
-      <c r="J96" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K96" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L96" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L96" s="0"/>
       <c r="M96" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N96" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O96" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P96" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q96" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5325,23 +6617,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H97" s="0" t="n">
+      <c r="H97" s="0" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="I97" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J97" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K97" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="I97" s="0"/>
-      <c r="J97" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K97" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L97" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L97" s="0"/>
       <c r="M97" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N97" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O97" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P97" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q97" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5377,23 +6682,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H98" s="0" t="n">
+      <c r="H98" s="0" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="I98" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J98" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K98" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="I98" s="0"/>
-      <c r="J98" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K98" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L98" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L98" s="0"/>
       <c r="M98" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N98" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O98" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P98" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q98" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5429,23 +6747,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H99" s="0" t="n">
+      <c r="H99" s="0" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="I99" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J99" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K99" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I99" s="0"/>
-      <c r="J99" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K99" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L99" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L99" s="0"/>
       <c r="M99" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N99" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O99" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P99" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q99" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5481,23 +6812,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H100" s="0" t="n">
+      <c r="H100" s="0" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="I100" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J100" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K100" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="I100" s="0"/>
-      <c r="J100" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K100" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L100" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L100" s="0"/>
       <c r="M100" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N100" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O100" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P100" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q100" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5533,23 +6877,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H101" s="0" t="n">
+      <c r="H101" s="0" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="I101" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J101" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K101" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="I101" s="0"/>
-      <c r="J101" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K101" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L101" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L101" s="0"/>
       <c r="M101" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N101" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O101" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P101" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q101" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5585,23 +6942,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H102" s="0" t="n">
+      <c r="H102" s="0" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="I102" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J102" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K102" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I102" s="0"/>
-      <c r="J102" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K102" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L102" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L102" s="0"/>
       <c r="M102" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N102" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O102" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P102" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q102" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5637,23 +7007,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H103" s="0" t="n">
+      <c r="H103" s="0" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="I103" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J103" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K103" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="I103" s="0"/>
-      <c r="J103" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K103" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L103" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L103" s="0"/>
       <c r="M103" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N103" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O103" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P103" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q103" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5689,23 +7072,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H104" s="0" t="n">
+      <c r="H104" s="0" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="I104" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J104" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K104" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I104" s="0"/>
-      <c r="J104" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K104" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L104" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L104" s="0"/>
       <c r="M104" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N104" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O104" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P104" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q104" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5741,23 +7137,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H105" s="0" t="n">
+      <c r="H105" s="0" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="I105" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J105" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K105" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I105" s="0"/>
-      <c r="J105" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K105" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L105" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L105" s="0"/>
       <c r="M105" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N105" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O105" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P105" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q105" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5793,23 +7202,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H106" s="0" t="n">
+      <c r="H106" s="0" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="I106" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J106" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K106" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="I106" s="0"/>
-      <c r="J106" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K106" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L106" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L106" s="0"/>
       <c r="M106" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N106" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O106" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P106" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q106" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5845,23 +7267,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H107" s="0" t="n">
+      <c r="H107" s="0" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="I107" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J107" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K107" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="I107" s="0"/>
-      <c r="J107" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K107" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L107" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L107" s="0"/>
       <c r="M107" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N107" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O107" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P107" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q107" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5897,23 +7332,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H108" s="0" t="n">
+      <c r="H108" s="0" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="I108" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J108" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K108" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="I108" s="0"/>
-      <c r="J108" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K108" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L108" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L108" s="0"/>
       <c r="M108" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N108" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O108" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P108" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q108" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5949,23 +7397,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H109" s="0" t="n">
+      <c r="H109" s="0" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="I109" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J109" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K109" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I109" s="0"/>
-      <c r="J109" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K109" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L109" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L109" s="0"/>
       <c r="M109" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N109" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O109" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P109" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q109" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6001,23 +7462,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H110" s="0" t="n">
+      <c r="H110" s="0" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="I110" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J110" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K110" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I110" s="0"/>
-      <c r="J110" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K110" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L110" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L110" s="0"/>
       <c r="M110" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N110" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O110" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P110" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q110" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6053,23 +7527,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H111" s="0" t="n">
+      <c r="H111" s="0" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="I111" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J111" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K111" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="I111" s="0"/>
-      <c r="J111" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K111" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L111" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L111" s="0"/>
       <c r="M111" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N111" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O111" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P111" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q111" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6105,23 +7592,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H112" s="0" t="n">
+      <c r="H112" s="0" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="I112" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J112" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K112" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="I112" s="0"/>
-      <c r="J112" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K112" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L112" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L112" s="0"/>
       <c r="M112" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N112" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O112" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P112" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q112" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6157,23 +7657,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H113" s="0" t="n">
+      <c r="H113" s="0" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="I113" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J113" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K113" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I113" s="0"/>
-      <c r="J113" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K113" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L113" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L113" s="0"/>
       <c r="M113" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N113" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O113" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P113" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q113" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6209,23 +7722,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H114" s="0" t="n">
+      <c r="H114" s="0" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="I114" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J114" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K114" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I114" s="0"/>
-      <c r="J114" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K114" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L114" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L114" s="0"/>
       <c r="M114" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N114" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O114" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P114" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q114" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6261,23 +7787,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H115" s="0" t="n">
+      <c r="H115" s="0" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="I115" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J115" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K115" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="I115" s="0"/>
-      <c r="J115" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K115" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L115" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L115" s="0"/>
       <c r="M115" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N115" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O115" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P115" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q115" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6313,23 +7852,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H116" s="0" t="n">
+      <c r="H116" s="0" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="I116" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J116" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K116" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="I116" s="0"/>
-      <c r="J116" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K116" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L116" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L116" s="0"/>
       <c r="M116" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N116" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O116" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P116" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q116" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6365,23 +7917,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H117" s="0" t="n">
+      <c r="H117" s="0" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="I117" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J117" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K117" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I117" s="0"/>
-      <c r="J117" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K117" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L117" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L117" s="0"/>
       <c r="M117" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N117" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O117" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P117" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q117" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6417,23 +7982,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H118" s="0" t="n">
+      <c r="H118" s="0" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="I118" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J118" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K118" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I118" s="0"/>
-      <c r="J118" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K118" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L118" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L118" s="0"/>
       <c r="M118" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N118" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O118" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P118" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q118" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6469,23 +8047,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H119" s="0" t="n">
+      <c r="H119" s="0" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="I119" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J119" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K119" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="I119" s="0"/>
-      <c r="J119" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K119" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L119" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L119" s="0"/>
       <c r="M119" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N119" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O119" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P119" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q119" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6521,23 +8112,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H120" s="0" t="n">
+      <c r="H120" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I120" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J120" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K120" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I120" s="0"/>
-      <c r="J120" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K120" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L120" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L120" s="0"/>
       <c r="M120" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N120" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O120" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P120" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q120" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6573,23 +8177,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H121" s="0" t="n">
+      <c r="H121" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I121" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J121" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K121" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="I121" s="0"/>
-      <c r="J121" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K121" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L121" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L121" s="0"/>
       <c r="M121" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N121" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O121" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P121" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q121" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6625,23 +8242,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H122" s="0" t="n">
+      <c r="H122" s="0" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="I122" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J122" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K122" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="I122" s="0"/>
-      <c r="J122" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K122" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L122" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L122" s="0"/>
       <c r="M122" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N122" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O122" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P122" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q122" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6677,23 +8307,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H123" s="0" t="n">
+      <c r="H123" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I123" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J123" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K123" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="I123" s="0"/>
-      <c r="J123" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K123" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L123" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L123" s="0"/>
       <c r="M123" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N123" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O123" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P123" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q123" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6729,23 +8372,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H124" s="0" t="n">
+      <c r="H124" s="0" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="I124" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J124" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K124" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I124" s="0"/>
-      <c r="J124" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K124" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L124" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L124" s="0"/>
       <c r="M124" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N124" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O124" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P124" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q124" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6781,23 +8437,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H125" s="0" t="n">
+      <c r="H125" s="0" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="I125" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J125" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K125" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I125" s="0"/>
-      <c r="J125" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K125" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L125" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L125" s="0"/>
       <c r="M125" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N125" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O125" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P125" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q125" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6833,23 +8502,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H126" s="0" t="n">
+      <c r="H126" s="0" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="I126" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J126" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K126" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I126" s="0"/>
-      <c r="J126" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K126" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L126" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L126" s="0"/>
       <c r="M126" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N126" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O126" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P126" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q126" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6885,23 +8567,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H127" s="0" t="n">
+      <c r="H127" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I127" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J127" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K127" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I127" s="0"/>
-      <c r="J127" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K127" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L127" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L127" s="0"/>
       <c r="M127" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N127" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O127" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P127" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q127" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6937,23 +8632,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H128" s="0" t="n">
+      <c r="H128" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I128" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J128" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K128" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="I128" s="0"/>
-      <c r="J128" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K128" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L128" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L128" s="0"/>
       <c r="M128" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N128" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O128" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P128" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q128" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6989,23 +8697,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H129" s="0" t="n">
+      <c r="H129" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I129" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J129" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K129" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="I129" s="0"/>
-      <c r="J129" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K129" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L129" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L129" s="0"/>
       <c r="M129" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N129" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O129" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P129" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q129" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7041,23 +8762,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H130" s="0" t="n">
+      <c r="H130" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I130" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J130" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K130" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="I130" s="0"/>
-      <c r="J130" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K130" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L130" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L130" s="0"/>
       <c r="M130" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N130" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O130" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P130" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q130" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7093,23 +8827,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H131" s="0" t="n">
+      <c r="H131" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I131" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J131" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K131" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I131" s="0"/>
-      <c r="J131" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K131" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L131" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L131" s="0"/>
       <c r="M131" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N131" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O131" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P131" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q131" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7145,23 +8892,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H132" s="0" t="n">
+      <c r="H132" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I132" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J132" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K132" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="I132" s="0"/>
-      <c r="J132" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K132" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L132" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L132" s="0"/>
       <c r="M132" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N132" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O132" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P132" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q132" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7197,23 +8957,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H133" s="0" t="n">
+      <c r="H133" s="0" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="I133" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J133" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K133" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I133" s="0"/>
-      <c r="J133" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K133" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L133" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L133" s="0"/>
       <c r="M133" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N133" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O133" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P133" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q133" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7249,23 +9022,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H134" s="0" t="n">
+      <c r="H134" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I134" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J134" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K134" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I134" s="0"/>
-      <c r="J134" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K134" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L134" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L134" s="0"/>
       <c r="M134" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N134" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O134" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P134" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q134" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7301,23 +9087,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H135" s="0" t="n">
+      <c r="H135" s="0" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="I135" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J135" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K135" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="I135" s="0"/>
-      <c r="J135" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K135" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L135" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L135" s="0"/>
       <c r="M135" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N135" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O135" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P135" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q135" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7353,23 +9152,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H136" s="0" t="n">
+      <c r="H136" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I136" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J136" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K136" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="I136" s="0"/>
-      <c r="J136" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K136" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L136" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L136" s="0"/>
       <c r="M136" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N136" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O136" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P136" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q136" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7405,23 +9217,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H137" s="0" t="n">
+      <c r="H137" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I137" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J137" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K137" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="I137" s="0"/>
-      <c r="J137" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K137" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L137" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L137" s="0"/>
       <c r="M137" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N137" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O137" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P137" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q137" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7457,23 +9282,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H138" s="0" t="n">
+      <c r="H138" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I138" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J138" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K138" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I138" s="0"/>
-      <c r="J138" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K138" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L138" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L138" s="0"/>
       <c r="M138" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N138" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O138" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P138" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q138" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7508,14 +9346,17 @@
         </is>
       </c>
       <c r="H139" s="0"/>
-      <c r="I139" s="0" t="n">
-        <v>65</v>
-      </c>
+      <c r="I139" s="0"/>
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
-      <c r="L139" s="0"/>
+      <c r="L139" s="0" t="n">
+        <v>66</v>
+      </c>
       <c r="M139" s="0"/>
       <c r="N139" s="0"/>
+      <c r="O139" s="0"/>
+      <c r="P139" s="0"/>
+      <c r="Q139" s="0"/>
     </row>
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
@@ -7548,14 +9389,17 @@
         </is>
       </c>
       <c r="H140" s="0"/>
-      <c r="I140" s="0" t="n">
-        <v>65</v>
-      </c>
+      <c r="I140" s="0"/>
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
-      <c r="L140" s="0"/>
+      <c r="L140" s="0" t="n">
+        <v>66</v>
+      </c>
       <c r="M140" s="0"/>
       <c r="N140" s="0"/>
+      <c r="O140" s="0"/>
+      <c r="P140" s="0"/>
+      <c r="Q140" s="0"/>
     </row>
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
@@ -7588,14 +9432,17 @@
         </is>
       </c>
       <c r="H141" s="0"/>
-      <c r="I141" s="0" t="n">
-        <v>65</v>
-      </c>
+      <c r="I141" s="0"/>
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
-      <c r="L141" s="0"/>
+      <c r="L141" s="0" t="n">
+        <v>66</v>
+      </c>
       <c r="M141" s="0"/>
       <c r="N141" s="0"/>
+      <c r="O141" s="0"/>
+      <c r="P141" s="0"/>
+      <c r="Q141" s="0"/>
     </row>
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
@@ -7628,14 +9475,17 @@
         </is>
       </c>
       <c r="H142" s="0"/>
-      <c r="I142" s="0" t="n">
-        <v>65</v>
-      </c>
+      <c r="I142" s="0"/>
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
-      <c r="L142" s="0"/>
+      <c r="L142" s="0" t="n">
+        <v>66</v>
+      </c>
       <c r="M142" s="0"/>
       <c r="N142" s="0"/>
+      <c r="O142" s="0"/>
+      <c r="P142" s="0"/>
+      <c r="Q142" s="0"/>
     </row>
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
@@ -7668,14 +9518,17 @@
         </is>
       </c>
       <c r="H143" s="0"/>
-      <c r="I143" s="0" t="n">
-        <v>65</v>
-      </c>
+      <c r="I143" s="0"/>
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
-      <c r="L143" s="0"/>
+      <c r="L143" s="0" t="n">
+        <v>66</v>
+      </c>
       <c r="M143" s="0"/>
       <c r="N143" s="0"/>
+      <c r="O143" s="0"/>
+      <c r="P143" s="0"/>
+      <c r="Q143" s="0"/>
     </row>
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
@@ -7709,23 +9562,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H144" s="0" t="n">
+      <c r="H144" s="0" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="I144" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J144" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K144" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I144" s="0"/>
-      <c r="J144" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K144" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L144" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L144" s="0"/>
       <c r="M144" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N144" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O144" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P144" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q144" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7761,23 +9627,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H145" s="0" t="n">
+      <c r="H145" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I145" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J145" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K145" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I145" s="0"/>
-      <c r="J145" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K145" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L145" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L145" s="0"/>
       <c r="M145" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N145" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O145" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P145" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q145" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7812,14 +9691,17 @@
         </is>
       </c>
       <c r="H146" s="0"/>
-      <c r="I146" s="0" t="n">
-        <v>64</v>
-      </c>
+      <c r="I146" s="0"/>
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
-      <c r="L146" s="0"/>
+      <c r="L146" s="0" t="n">
+        <v>65</v>
+      </c>
       <c r="M146" s="0"/>
       <c r="N146" s="0"/>
+      <c r="O146" s="0"/>
+      <c r="P146" s="0"/>
+      <c r="Q146" s="0"/>
     </row>
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
@@ -7853,23 +9735,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H147" s="0" t="n">
+      <c r="H147" s="0" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="I147" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J147" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K147" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="I147" s="0"/>
-      <c r="J147" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K147" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L147" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L147" s="0"/>
       <c r="M147" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N147" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O147" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P147" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q147" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7904,14 +9799,17 @@
         </is>
       </c>
       <c r="H148" s="0"/>
-      <c r="I148" s="0" t="n">
-        <v>63</v>
-      </c>
+      <c r="I148" s="0"/>
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
-      <c r="L148" s="0"/>
+      <c r="L148" s="0" t="n">
+        <v>64</v>
+      </c>
       <c r="M148" s="0"/>
       <c r="N148" s="0"/>
+      <c r="O148" s="0"/>
+      <c r="P148" s="0"/>
+      <c r="Q148" s="0"/>
     </row>
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
@@ -7945,23 +9843,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H149" s="0" t="n">
+      <c r="H149" s="0" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="I149" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J149" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K149" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I149" s="0"/>
-      <c r="J149" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K149" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L149" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L149" s="0"/>
       <c r="M149" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N149" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O149" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P149" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q149" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7997,23 +9908,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H150" s="0" t="n">
+      <c r="H150" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I150" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J150" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K150" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="I150" s="0"/>
-      <c r="J150" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K150" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L150" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L150" s="0"/>
       <c r="M150" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N150" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O150" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P150" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q150" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8049,23 +9973,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H151" s="0" t="n">
+      <c r="H151" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I151" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J151" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K151" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I151" s="0"/>
-      <c r="J151" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K151" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L151" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L151" s="0"/>
       <c r="M151" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N151" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O151" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P151" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q151" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8101,23 +10038,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H152" s="0" t="n">
+      <c r="H152" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I152" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J152" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K152" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I152" s="0"/>
-      <c r="J152" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K152" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L152" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L152" s="0"/>
       <c r="M152" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N152" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O152" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P152" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q152" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8153,23 +10103,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H153" s="0" t="n">
+      <c r="H153" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I153" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J153" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K153" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I153" s="0"/>
-      <c r="J153" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K153" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L153" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L153" s="0"/>
       <c r="M153" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N153" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O153" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P153" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q153" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8204,14 +10167,17 @@
         </is>
       </c>
       <c r="H154" s="0"/>
-      <c r="I154" s="0" t="n">
-        <v>61</v>
-      </c>
+      <c r="I154" s="0"/>
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
-      <c r="L154" s="0"/>
+      <c r="L154" s="0" t="n">
+        <v>62</v>
+      </c>
       <c r="M154" s="0"/>
       <c r="N154" s="0"/>
+      <c r="O154" s="0"/>
+      <c r="P154" s="0"/>
+      <c r="Q154" s="0"/>
     </row>
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
@@ -8245,23 +10211,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H155" s="0" t="n">
+      <c r="H155" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I155" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J155" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K155" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I155" s="0"/>
-      <c r="J155" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K155" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L155" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L155" s="0"/>
       <c r="M155" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N155" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O155" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P155" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q155" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8296,14 +10275,17 @@
         </is>
       </c>
       <c r="H156" s="0"/>
-      <c r="I156" s="0" t="n">
-        <v>60</v>
-      </c>
+      <c r="I156" s="0"/>
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
-      <c r="L156" s="0"/>
+      <c r="L156" s="0" t="n">
+        <v>61</v>
+      </c>
       <c r="M156" s="0"/>
       <c r="N156" s="0"/>
+      <c r="O156" s="0"/>
+      <c r="P156" s="0"/>
+      <c r="Q156" s="0"/>
     </row>
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
@@ -8337,23 +10319,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H157" s="0" t="n">
+      <c r="H157" s="0" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="I157" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J157" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K157" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I157" s="0"/>
-      <c r="J157" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K157" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L157" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L157" s="0"/>
       <c r="M157" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N157" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O157" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P157" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q157" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8389,23 +10384,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H158" s="0" t="n">
+      <c r="H158" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I158" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J158" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K158" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I158" s="0"/>
-      <c r="J158" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K158" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L158" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L158" s="0"/>
       <c r="M158" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N158" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O158" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P158" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q158" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8440,14 +10448,17 @@
         </is>
       </c>
       <c r="H159" s="0"/>
-      <c r="I159" s="0" t="n">
-        <v>57</v>
-      </c>
+      <c r="I159" s="0"/>
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
-      <c r="L159" s="0"/>
+      <c r="L159" s="0" t="n">
+        <v>58</v>
+      </c>
       <c r="M159" s="0"/>
       <c r="N159" s="0"/>
+      <c r="O159" s="0"/>
+      <c r="P159" s="0"/>
+      <c r="Q159" s="0"/>
     </row>
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
@@ -8481,23 +10492,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H160" s="0" t="n">
+      <c r="H160" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I160" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J160" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K160" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="I160" s="0"/>
-      <c r="J160" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K160" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L160" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L160" s="0"/>
       <c r="M160" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N160" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O160" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P160" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q160" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8533,23 +10557,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H161" s="0" t="n">
+      <c r="H161" s="0" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="I161" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J161" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K161" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I161" s="0"/>
-      <c r="J161" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K161" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L161" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L161" s="0"/>
       <c r="M161" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N161" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O161" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P161" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q161" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8584,14 +10621,17 @@
         </is>
       </c>
       <c r="H162" s="0"/>
-      <c r="I162" s="0" t="n">
-        <v>54</v>
-      </c>
+      <c r="I162" s="0"/>
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
-      <c r="L162" s="0"/>
+      <c r="L162" s="0" t="n">
+        <v>55</v>
+      </c>
       <c r="M162" s="0"/>
       <c r="N162" s="0"/>
+      <c r="O162" s="0"/>
+      <c r="P162" s="0"/>
+      <c r="Q162" s="0"/>
     </row>
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
@@ -8624,14 +10664,17 @@
         </is>
       </c>
       <c r="H163" s="0"/>
-      <c r="I163" s="0" t="n">
-        <v>54</v>
-      </c>
+      <c r="I163" s="0"/>
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
-      <c r="L163" s="0"/>
+      <c r="L163" s="0" t="n">
+        <v>55</v>
+      </c>
       <c r="M163" s="0"/>
       <c r="N163" s="0"/>
+      <c r="O163" s="0"/>
+      <c r="P163" s="0"/>
+      <c r="Q163" s="0"/>
     </row>
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
@@ -8664,14 +10707,17 @@
         </is>
       </c>
       <c r="H164" s="0"/>
-      <c r="I164" s="0" t="n">
-        <v>54</v>
-      </c>
+      <c r="I164" s="0"/>
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
-      <c r="L164" s="0"/>
+      <c r="L164" s="0" t="n">
+        <v>55</v>
+      </c>
       <c r="M164" s="0"/>
       <c r="N164" s="0"/>
+      <c r="O164" s="0"/>
+      <c r="P164" s="0"/>
+      <c r="Q164" s="0"/>
     </row>
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
@@ -8704,14 +10750,17 @@
         </is>
       </c>
       <c r="H165" s="0"/>
-      <c r="I165" s="0" t="n">
-        <v>53</v>
-      </c>
+      <c r="I165" s="0"/>
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
-      <c r="L165" s="0"/>
+      <c r="L165" s="0" t="n">
+        <v>54</v>
+      </c>
       <c r="M165" s="0"/>
       <c r="N165" s="0"/>
+      <c r="O165" s="0"/>
+      <c r="P165" s="0"/>
+      <c r="Q165" s="0"/>
     </row>
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
@@ -8744,14 +10793,17 @@
         </is>
       </c>
       <c r="H166" s="0"/>
-      <c r="I166" s="0" t="n">
-        <v>52</v>
-      </c>
+      <c r="I166" s="0"/>
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
-      <c r="L166" s="0"/>
+      <c r="L166" s="0" t="n">
+        <v>53</v>
+      </c>
       <c r="M166" s="0"/>
       <c r="N166" s="0"/>
+      <c r="O166" s="0"/>
+      <c r="P166" s="0"/>
+      <c r="Q166" s="0"/>
     </row>
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
@@ -8784,14 +10836,17 @@
         </is>
       </c>
       <c r="H167" s="0"/>
-      <c r="I167" s="0" t="n">
-        <v>51</v>
-      </c>
+      <c r="I167" s="0"/>
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
-      <c r="L167" s="0"/>
+      <c r="L167" s="0" t="n">
+        <v>52</v>
+      </c>
       <c r="M167" s="0"/>
       <c r="N167" s="0"/>
+      <c r="O167" s="0"/>
+      <c r="P167" s="0"/>
+      <c r="Q167" s="0"/>
     </row>
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
@@ -8824,14 +10879,17 @@
         </is>
       </c>
       <c r="H168" s="0"/>
-      <c r="I168" s="0" t="n">
-        <v>51</v>
-      </c>
+      <c r="I168" s="0"/>
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
-      <c r="L168" s="0"/>
+      <c r="L168" s="0" t="n">
+        <v>52</v>
+      </c>
       <c r="M168" s="0"/>
       <c r="N168" s="0"/>
+      <c r="O168" s="0"/>
+      <c r="P168" s="0"/>
+      <c r="Q168" s="0"/>
     </row>
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
@@ -8864,14 +10922,17 @@
         </is>
       </c>
       <c r="H169" s="0"/>
-      <c r="I169" s="0" t="n">
-        <v>51</v>
-      </c>
+      <c r="I169" s="0"/>
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
-      <c r="L169" s="0"/>
+      <c r="L169" s="0" t="n">
+        <v>52</v>
+      </c>
       <c r="M169" s="0"/>
       <c r="N169" s="0"/>
+      <c r="O169" s="0"/>
+      <c r="P169" s="0"/>
+      <c r="Q169" s="0"/>
     </row>
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
@@ -8904,14 +10965,17 @@
         </is>
       </c>
       <c r="H170" s="0"/>
-      <c r="I170" s="0" t="n">
-        <v>49</v>
-      </c>
+      <c r="I170" s="0"/>
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
-      <c r="L170" s="0"/>
+      <c r="L170" s="0" t="n">
+        <v>50</v>
+      </c>
       <c r="M170" s="0"/>
       <c r="N170" s="0"/>
+      <c r="O170" s="0"/>
+      <c r="P170" s="0"/>
+      <c r="Q170" s="0"/>
     </row>
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
@@ -8944,14 +11008,17 @@
         </is>
       </c>
       <c r="H171" s="0"/>
-      <c r="I171" s="0" t="n">
-        <v>48</v>
-      </c>
+      <c r="I171" s="0"/>
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
-      <c r="L171" s="0"/>
+      <c r="L171" s="0" t="n">
+        <v>49</v>
+      </c>
       <c r="M171" s="0"/>
       <c r="N171" s="0"/>
+      <c r="O171" s="0"/>
+      <c r="P171" s="0"/>
+      <c r="Q171" s="0"/>
     </row>
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
@@ -8984,14 +11051,17 @@
         </is>
       </c>
       <c r="H172" s="0"/>
-      <c r="I172" s="0" t="n">
-        <v>47</v>
-      </c>
+      <c r="I172" s="0"/>
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
-      <c r="L172" s="0"/>
+      <c r="L172" s="0" t="n">
+        <v>48</v>
+      </c>
       <c r="M172" s="0"/>
       <c r="N172" s="0"/>
+      <c r="O172" s="0"/>
+      <c r="P172" s="0"/>
+      <c r="Q172" s="0"/>
     </row>
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
@@ -9024,14 +11094,17 @@
         </is>
       </c>
       <c r="H173" s="0"/>
-      <c r="I173" s="0" t="n">
-        <v>47</v>
-      </c>
+      <c r="I173" s="0"/>
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
-      <c r="L173" s="0"/>
+      <c r="L173" s="0" t="n">
+        <v>48</v>
+      </c>
       <c r="M173" s="0"/>
       <c r="N173" s="0"/>
+      <c r="O173" s="0"/>
+      <c r="P173" s="0"/>
+      <c r="Q173" s="0"/>
     </row>
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
@@ -9064,14 +11137,17 @@
         </is>
       </c>
       <c r="H174" s="0"/>
-      <c r="I174" s="0" t="n">
-        <v>47</v>
-      </c>
+      <c r="I174" s="0"/>
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
-      <c r="L174" s="0"/>
+      <c r="L174" s="0" t="n">
+        <v>48</v>
+      </c>
       <c r="M174" s="0"/>
       <c r="N174" s="0"/>
+      <c r="O174" s="0"/>
+      <c r="P174" s="0"/>
+      <c r="Q174" s="0"/>
     </row>
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
@@ -9104,14 +11180,17 @@
         </is>
       </c>
       <c r="H175" s="0"/>
-      <c r="I175" s="0" t="n">
-        <v>46</v>
-      </c>
+      <c r="I175" s="0"/>
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
-      <c r="L175" s="0"/>
+      <c r="L175" s="0" t="n">
+        <v>47</v>
+      </c>
       <c r="M175" s="0"/>
       <c r="N175" s="0"/>
+      <c r="O175" s="0"/>
+      <c r="P175" s="0"/>
+      <c r="Q175" s="0"/>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
@@ -9144,14 +11223,17 @@
         </is>
       </c>
       <c r="H176" s="0"/>
-      <c r="I176" s="0" t="n">
-        <v>46</v>
-      </c>
+      <c r="I176" s="0"/>
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
-      <c r="L176" s="0"/>
+      <c r="L176" s="0" t="n">
+        <v>47</v>
+      </c>
       <c r="M176" s="0"/>
       <c r="N176" s="0"/>
+      <c r="O176" s="0"/>
+      <c r="P176" s="0"/>
+      <c r="Q176" s="0"/>
     </row>
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
@@ -9184,14 +11266,17 @@
         </is>
       </c>
       <c r="H177" s="0"/>
-      <c r="I177" s="0" t="n">
-        <v>45</v>
-      </c>
+      <c r="I177" s="0"/>
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
-      <c r="L177" s="0"/>
+      <c r="L177" s="0" t="n">
+        <v>46</v>
+      </c>
       <c r="M177" s="0"/>
       <c r="N177" s="0"/>
+      <c r="O177" s="0"/>
+      <c r="P177" s="0"/>
+      <c r="Q177" s="0"/>
     </row>
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
@@ -9224,14 +11309,17 @@
         </is>
       </c>
       <c r="H178" s="0"/>
-      <c r="I178" s="0" t="n">
-        <v>45</v>
-      </c>
+      <c r="I178" s="0"/>
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
-      <c r="L178" s="0"/>
+      <c r="L178" s="0" t="n">
+        <v>46</v>
+      </c>
       <c r="M178" s="0"/>
       <c r="N178" s="0"/>
+      <c r="O178" s="0"/>
+      <c r="P178" s="0"/>
+      <c r="Q178" s="0"/>
     </row>
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
@@ -9264,14 +11352,17 @@
         </is>
       </c>
       <c r="H179" s="0"/>
-      <c r="I179" s="0" t="n">
-        <v>44</v>
-      </c>
+      <c r="I179" s="0"/>
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
-      <c r="L179" s="0"/>
+      <c r="L179" s="0" t="n">
+        <v>45</v>
+      </c>
       <c r="M179" s="0"/>
       <c r="N179" s="0"/>
+      <c r="O179" s="0"/>
+      <c r="P179" s="0"/>
+      <c r="Q179" s="0"/>
     </row>
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
@@ -9304,14 +11395,17 @@
         </is>
       </c>
       <c r="H180" s="0"/>
-      <c r="I180" s="0" t="n">
-        <v>44</v>
-      </c>
+      <c r="I180" s="0"/>
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
-      <c r="L180" s="0"/>
+      <c r="L180" s="0" t="n">
+        <v>45</v>
+      </c>
       <c r="M180" s="0"/>
       <c r="N180" s="0"/>
+      <c r="O180" s="0"/>
+      <c r="P180" s="0"/>
+      <c r="Q180" s="0"/>
     </row>
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
@@ -9344,14 +11438,17 @@
         </is>
       </c>
       <c r="H181" s="0"/>
-      <c r="I181" s="0" t="n">
-        <v>43</v>
-      </c>
+      <c r="I181" s="0"/>
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
-      <c r="L181" s="0"/>
+      <c r="L181" s="0" t="n">
+        <v>44</v>
+      </c>
       <c r="M181" s="0"/>
       <c r="N181" s="0"/>
+      <c r="O181" s="0"/>
+      <c r="P181" s="0"/>
+      <c r="Q181" s="0"/>
     </row>
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
@@ -9384,14 +11481,17 @@
         </is>
       </c>
       <c r="H182" s="0"/>
-      <c r="I182" s="0" t="n">
-        <v>42</v>
-      </c>
+      <c r="I182" s="0"/>
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
-      <c r="L182" s="0"/>
+      <c r="L182" s="0" t="n">
+        <v>43</v>
+      </c>
       <c r="M182" s="0"/>
       <c r="N182" s="0"/>
+      <c r="O182" s="0"/>
+      <c r="P182" s="0"/>
+      <c r="Q182" s="0"/>
     </row>
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
@@ -9424,14 +11524,17 @@
         </is>
       </c>
       <c r="H183" s="0"/>
-      <c r="I183" s="0" t="n">
-        <v>41</v>
-      </c>
+      <c r="I183" s="0"/>
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
-      <c r="L183" s="0"/>
+      <c r="L183" s="0" t="n">
+        <v>42</v>
+      </c>
       <c r="M183" s="0"/>
       <c r="N183" s="0"/>
+      <c r="O183" s="0"/>
+      <c r="P183" s="0"/>
+      <c r="Q183" s="0"/>
     </row>
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
@@ -9464,14 +11567,17 @@
         </is>
       </c>
       <c r="H184" s="0"/>
-      <c r="I184" s="0" t="n">
-        <v>40</v>
-      </c>
+      <c r="I184" s="0"/>
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
-      <c r="L184" s="0"/>
+      <c r="L184" s="0" t="n">
+        <v>41</v>
+      </c>
       <c r="M184" s="0"/>
       <c r="N184" s="0"/>
+      <c r="O184" s="0"/>
+      <c r="P184" s="0"/>
+      <c r="Q184" s="0"/>
     </row>
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
@@ -9504,14 +11610,17 @@
         </is>
       </c>
       <c r="H185" s="0"/>
-      <c r="I185" s="0" t="n">
-        <v>39</v>
-      </c>
+      <c r="I185" s="0"/>
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
-      <c r="L185" s="0"/>
+      <c r="L185" s="0" t="n">
+        <v>40</v>
+      </c>
       <c r="M185" s="0"/>
       <c r="N185" s="0"/>
+      <c r="O185" s="0"/>
+      <c r="P185" s="0"/>
+      <c r="Q185" s="0"/>
     </row>
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
@@ -9544,14 +11653,17 @@
         </is>
       </c>
       <c r="H186" s="0"/>
-      <c r="I186" s="0" t="n">
-        <v>39</v>
-      </c>
+      <c r="I186" s="0"/>
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
-      <c r="L186" s="0"/>
+      <c r="L186" s="0" t="n">
+        <v>40</v>
+      </c>
       <c r="M186" s="0"/>
       <c r="N186" s="0"/>
+      <c r="O186" s="0"/>
+      <c r="P186" s="0"/>
+      <c r="Q186" s="0"/>
     </row>
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
@@ -9584,14 +11696,17 @@
         </is>
       </c>
       <c r="H187" s="0"/>
-      <c r="I187" s="0" t="n">
-        <v>38</v>
-      </c>
+      <c r="I187" s="0"/>
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
-      <c r="L187" s="0"/>
+      <c r="L187" s="0" t="n">
+        <v>39</v>
+      </c>
       <c r="M187" s="0"/>
       <c r="N187" s="0"/>
+      <c r="O187" s="0"/>
+      <c r="P187" s="0"/>
+      <c r="Q187" s="0"/>
     </row>
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
@@ -9624,14 +11739,17 @@
         </is>
       </c>
       <c r="H188" s="0"/>
-      <c r="I188" s="0" t="n">
-        <v>37</v>
-      </c>
+      <c r="I188" s="0"/>
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
-      <c r="L188" s="0"/>
+      <c r="L188" s="0" t="n">
+        <v>38</v>
+      </c>
       <c r="M188" s="0"/>
       <c r="N188" s="0"/>
+      <c r="O188" s="0"/>
+      <c r="P188" s="0"/>
+      <c r="Q188" s="0"/>
     </row>
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
@@ -9664,14 +11782,17 @@
         </is>
       </c>
       <c r="H189" s="0"/>
-      <c r="I189" s="0" t="n">
-        <v>36</v>
-      </c>
+      <c r="I189" s="0"/>
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
-      <c r="L189" s="0"/>
+      <c r="L189" s="0" t="n">
+        <v>37</v>
+      </c>
       <c r="M189" s="0"/>
       <c r="N189" s="0"/>
+      <c r="O189" s="0"/>
+      <c r="P189" s="0"/>
+      <c r="Q189" s="0"/>
     </row>
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
@@ -9704,14 +11825,17 @@
         </is>
       </c>
       <c r="H190" s="0"/>
-      <c r="I190" s="0" t="n">
-        <v>32</v>
-      </c>
+      <c r="I190" s="0"/>
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
-      <c r="L190" s="0"/>
+      <c r="L190" s="0" t="n">
+        <v>33</v>
+      </c>
       <c r="M190" s="0"/>
       <c r="N190" s="0"/>
+      <c r="O190" s="0"/>
+      <c r="P190" s="0"/>
+      <c r="Q190" s="0"/>
     </row>
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
@@ -9744,14 +11868,17 @@
         </is>
       </c>
       <c r="H191" s="0"/>
-      <c r="I191" s="0" t="n">
-        <v>31</v>
-      </c>
+      <c r="I191" s="0"/>
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
-      <c r="L191" s="0"/>
+      <c r="L191" s="0" t="n">
+        <v>32</v>
+      </c>
       <c r="M191" s="0"/>
       <c r="N191" s="0"/>
+      <c r="O191" s="0"/>
+      <c r="P191" s="0"/>
+      <c r="Q191" s="0"/>
     </row>
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
@@ -9784,14 +11911,17 @@
         </is>
       </c>
       <c r="H192" s="0"/>
-      <c r="I192" s="0" t="n">
-        <v>29</v>
-      </c>
+      <c r="I192" s="0"/>
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
-      <c r="L192" s="0"/>
+      <c r="L192" s="0" t="n">
+        <v>30</v>
+      </c>
       <c r="M192" s="0"/>
       <c r="N192" s="0"/>
+      <c r="O192" s="0"/>
+      <c r="P192" s="0"/>
+      <c r="Q192" s="0"/>
     </row>
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
@@ -9824,14 +11954,17 @@
         </is>
       </c>
       <c r="H193" s="0"/>
-      <c r="I193" s="0" t="n">
-        <v>28</v>
-      </c>
+      <c r="I193" s="0"/>
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
-      <c r="L193" s="0"/>
+      <c r="L193" s="0" t="n">
+        <v>29</v>
+      </c>
       <c r="M193" s="0"/>
       <c r="N193" s="0"/>
+      <c r="O193" s="0"/>
+      <c r="P193" s="0"/>
+      <c r="Q193" s="0"/>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
@@ -9864,14 +11997,17 @@
         </is>
       </c>
       <c r="H194" s="0"/>
-      <c r="I194" s="0" t="n">
-        <v>28</v>
-      </c>
+      <c r="I194" s="0"/>
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
-      <c r="L194" s="0"/>
+      <c r="L194" s="0" t="n">
+        <v>29</v>
+      </c>
       <c r="M194" s="0"/>
       <c r="N194" s="0"/>
+      <c r="O194" s="0"/>
+      <c r="P194" s="0"/>
+      <c r="Q194" s="0"/>
     </row>
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
@@ -9904,14 +12040,17 @@
         </is>
       </c>
       <c r="H195" s="0"/>
-      <c r="I195" s="0" t="n">
-        <v>27</v>
-      </c>
+      <c r="I195" s="0"/>
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
-      <c r="L195" s="0"/>
+      <c r="L195" s="0" t="n">
+        <v>28</v>
+      </c>
       <c r="M195" s="0"/>
       <c r="N195" s="0"/>
+      <c r="O195" s="0"/>
+      <c r="P195" s="0"/>
+      <c r="Q195" s="0"/>
     </row>
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
@@ -9944,14 +12083,17 @@
         </is>
       </c>
       <c r="H196" s="0"/>
-      <c r="I196" s="0" t="n">
-        <v>27</v>
-      </c>
+      <c r="I196" s="0"/>
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
-      <c r="L196" s="0"/>
+      <c r="L196" s="0" t="n">
+        <v>28</v>
+      </c>
       <c r="M196" s="0"/>
       <c r="N196" s="0"/>
+      <c r="O196" s="0"/>
+      <c r="P196" s="0"/>
+      <c r="Q196" s="0"/>
     </row>
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
@@ -9984,14 +12126,17 @@
         </is>
       </c>
       <c r="H197" s="0"/>
-      <c r="I197" s="0" t="n">
-        <v>27</v>
-      </c>
+      <c r="I197" s="0"/>
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
-      <c r="L197" s="0"/>
+      <c r="L197" s="0" t="n">
+        <v>28</v>
+      </c>
       <c r="M197" s="0"/>
       <c r="N197" s="0"/>
+      <c r="O197" s="0"/>
+      <c r="P197" s="0"/>
+      <c r="Q197" s="0"/>
     </row>
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
@@ -10024,14 +12169,17 @@
         </is>
       </c>
       <c r="H198" s="0"/>
-      <c r="I198" s="0" t="n">
-        <v>24</v>
-      </c>
+      <c r="I198" s="0"/>
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
-      <c r="L198" s="0"/>
+      <c r="L198" s="0" t="n">
+        <v>25</v>
+      </c>
       <c r="M198" s="0"/>
       <c r="N198" s="0"/>
+      <c r="O198" s="0"/>
+      <c r="P198" s="0"/>
+      <c r="Q198" s="0"/>
     </row>
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
@@ -10064,14 +12212,17 @@
         </is>
       </c>
       <c r="H199" s="0"/>
-      <c r="I199" s="0" t="n">
-        <v>22</v>
-      </c>
+      <c r="I199" s="0"/>
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
-      <c r="L199" s="0"/>
+      <c r="L199" s="0" t="n">
+        <v>23</v>
+      </c>
       <c r="M199" s="0"/>
       <c r="N199" s="0"/>
+      <c r="O199" s="0"/>
+      <c r="P199" s="0"/>
+      <c r="Q199" s="0"/>
     </row>
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
@@ -10104,14 +12255,17 @@
         </is>
       </c>
       <c r="H200" s="0"/>
-      <c r="I200" s="0" t="n">
-        <v>22</v>
-      </c>
+      <c r="I200" s="0"/>
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
-      <c r="L200" s="0"/>
+      <c r="L200" s="0" t="n">
+        <v>23</v>
+      </c>
       <c r="M200" s="0"/>
       <c r="N200" s="0"/>
+      <c r="O200" s="0"/>
+      <c r="P200" s="0"/>
+      <c r="Q200" s="0"/>
     </row>
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
@@ -10144,14 +12298,17 @@
         </is>
       </c>
       <c r="H201" s="0"/>
-      <c r="I201" s="0" t="n">
-        <v>22</v>
-      </c>
+      <c r="I201" s="0"/>
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
-      <c r="L201" s="0"/>
+      <c r="L201" s="0" t="n">
+        <v>23</v>
+      </c>
       <c r="M201" s="0"/>
       <c r="N201" s="0"/>
+      <c r="O201" s="0"/>
+      <c r="P201" s="0"/>
+      <c r="Q201" s="0"/>
     </row>
   </sheetData>
   <sheetCalcPr fullCalcOnLoad="1"/>
@@ -10174,7 +12331,7 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId13"/>
+  <drawing r:id="rId15"/>
 </worksheet>
 </file>
 
@@ -10190,7 +12347,7 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId14"/>
+  <drawing r:id="rId16"/>
 </worksheet>
 </file>
 
@@ -10206,7 +12363,7 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId15"/>
+  <drawing r:id="rId17"/>
 </worksheet>
 </file>
 
@@ -10222,7 +12379,7 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId16"/>
+  <drawing r:id="rId18"/>
 </worksheet>
 </file>
 
@@ -10238,6 +12395,22 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId17"/>
+  <drawing r:id="rId19"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId20"/>
 </worksheet>
 </file>
--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -9350,7 +9350,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M139" s="0"/>
       <c r="N139" s="0"/>
@@ -9393,7 +9393,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M140" s="0"/>
       <c r="N140" s="0"/>
@@ -9436,7 +9436,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M141" s="0"/>
       <c r="N141" s="0"/>
@@ -9479,7 +9479,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M142" s="0"/>
       <c r="N142" s="0"/>
@@ -9522,7 +9522,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M143" s="0"/>
       <c r="N143" s="0"/>
@@ -9695,7 +9695,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M146" s="0"/>
       <c r="N146" s="0"/>
@@ -9803,7 +9803,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M148" s="0"/>
       <c r="N148" s="0"/>
@@ -10171,7 +10171,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M154" s="0"/>
       <c r="N154" s="0"/>
@@ -10279,7 +10279,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M156" s="0"/>
       <c r="N156" s="0"/>
@@ -10452,7 +10452,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M159" s="0"/>
       <c r="N159" s="0"/>
@@ -10625,7 +10625,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M162" s="0"/>
       <c r="N162" s="0"/>
@@ -10668,7 +10668,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M163" s="0"/>
       <c r="N163" s="0"/>
@@ -10711,7 +10711,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M164" s="0"/>
       <c r="N164" s="0"/>
@@ -10754,7 +10754,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M165" s="0"/>
       <c r="N165" s="0"/>
@@ -10797,7 +10797,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M166" s="0"/>
       <c r="N166" s="0"/>
@@ -10840,7 +10840,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M167" s="0"/>
       <c r="N167" s="0"/>
@@ -10883,7 +10883,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M168" s="0"/>
       <c r="N168" s="0"/>
@@ -10926,7 +10926,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M169" s="0"/>
       <c r="N169" s="0"/>
@@ -10969,7 +10969,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M170" s="0"/>
       <c r="N170" s="0"/>
@@ -11012,7 +11012,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M171" s="0"/>
       <c r="N171" s="0"/>
@@ -11055,7 +11055,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M172" s="0"/>
       <c r="N172" s="0"/>
@@ -11098,7 +11098,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M173" s="0"/>
       <c r="N173" s="0"/>
@@ -11141,7 +11141,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M174" s="0"/>
       <c r="N174" s="0"/>
@@ -11184,7 +11184,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M175" s="0"/>
       <c r="N175" s="0"/>
@@ -11227,7 +11227,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M176" s="0"/>
       <c r="N176" s="0"/>
@@ -11270,7 +11270,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M177" s="0"/>
       <c r="N177" s="0"/>
@@ -11313,7 +11313,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M178" s="0"/>
       <c r="N178" s="0"/>
@@ -11356,7 +11356,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M179" s="0"/>
       <c r="N179" s="0"/>
@@ -11399,7 +11399,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M180" s="0"/>
       <c r="N180" s="0"/>
@@ -11442,7 +11442,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M181" s="0"/>
       <c r="N181" s="0"/>
@@ -11485,7 +11485,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M182" s="0"/>
       <c r="N182" s="0"/>
@@ -11528,7 +11528,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M183" s="0"/>
       <c r="N183" s="0"/>
@@ -11571,7 +11571,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M184" s="0"/>
       <c r="N184" s="0"/>
@@ -11614,7 +11614,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M185" s="0"/>
       <c r="N185" s="0"/>
@@ -11657,7 +11657,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M186" s="0"/>
       <c r="N186" s="0"/>
@@ -11700,7 +11700,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M187" s="0"/>
       <c r="N187" s="0"/>
@@ -11743,7 +11743,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M188" s="0"/>
       <c r="N188" s="0"/>
@@ -11786,7 +11786,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M189" s="0"/>
       <c r="N189" s="0"/>
@@ -11829,7 +11829,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M190" s="0"/>
       <c r="N190" s="0"/>
@@ -11872,7 +11872,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M191" s="0"/>
       <c r="N191" s="0"/>
@@ -11915,7 +11915,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M192" s="0"/>
       <c r="N192" s="0"/>
@@ -11958,7 +11958,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M193" s="0"/>
       <c r="N193" s="0"/>
@@ -12001,7 +12001,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M194" s="0"/>
       <c r="N194" s="0"/>
@@ -12044,7 +12044,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M195" s="0"/>
       <c r="N195" s="0"/>
@@ -12087,7 +12087,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M196" s="0"/>
       <c r="N196" s="0"/>
@@ -12130,7 +12130,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M197" s="0"/>
       <c r="N197" s="0"/>
@@ -12173,7 +12173,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M198" s="0"/>
       <c r="N198" s="0"/>
@@ -12216,7 +12216,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M199" s="0"/>
       <c r="N199" s="0"/>
@@ -12259,7 +12259,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M200" s="0"/>
       <c r="N200" s="0"/>
@@ -12302,7 +12302,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M201" s="0"/>
       <c r="N201" s="0"/>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -9350,7 +9350,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M139" s="0"/>
       <c r="N139" s="0"/>
@@ -9393,7 +9393,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M140" s="0"/>
       <c r="N140" s="0"/>
@@ -9436,7 +9436,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M141" s="0"/>
       <c r="N141" s="0"/>
@@ -9479,7 +9479,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M142" s="0"/>
       <c r="N142" s="0"/>
@@ -9522,7 +9522,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M143" s="0"/>
       <c r="N143" s="0"/>
@@ -9695,7 +9695,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M146" s="0"/>
       <c r="N146" s="0"/>
@@ -9803,7 +9803,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M148" s="0"/>
       <c r="N148" s="0"/>
@@ -10171,7 +10171,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M154" s="0"/>
       <c r="N154" s="0"/>
@@ -10279,7 +10279,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M156" s="0"/>
       <c r="N156" s="0"/>
@@ -10452,7 +10452,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M159" s="0"/>
       <c r="N159" s="0"/>
@@ -10625,7 +10625,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M162" s="0"/>
       <c r="N162" s="0"/>
@@ -10668,7 +10668,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M163" s="0"/>
       <c r="N163" s="0"/>
@@ -10711,7 +10711,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M164" s="0"/>
       <c r="N164" s="0"/>
@@ -10754,7 +10754,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M165" s="0"/>
       <c r="N165" s="0"/>
@@ -10797,7 +10797,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M166" s="0"/>
       <c r="N166" s="0"/>
@@ -10840,7 +10840,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M167" s="0"/>
       <c r="N167" s="0"/>
@@ -10883,7 +10883,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M168" s="0"/>
       <c r="N168" s="0"/>
@@ -10926,7 +10926,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M169" s="0"/>
       <c r="N169" s="0"/>
@@ -10969,7 +10969,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M170" s="0"/>
       <c r="N170" s="0"/>
@@ -11012,7 +11012,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M171" s="0"/>
       <c r="N171" s="0"/>
@@ -11055,7 +11055,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M172" s="0"/>
       <c r="N172" s="0"/>
@@ -11098,7 +11098,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M173" s="0"/>
       <c r="N173" s="0"/>
@@ -11141,7 +11141,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M174" s="0"/>
       <c r="N174" s="0"/>
@@ -11184,7 +11184,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M175" s="0"/>
       <c r="N175" s="0"/>
@@ -11227,7 +11227,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M176" s="0"/>
       <c r="N176" s="0"/>
@@ -11270,7 +11270,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M177" s="0"/>
       <c r="N177" s="0"/>
@@ -11313,7 +11313,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M178" s="0"/>
       <c r="N178" s="0"/>
@@ -11356,7 +11356,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M179" s="0"/>
       <c r="N179" s="0"/>
@@ -11399,7 +11399,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M180" s="0"/>
       <c r="N180" s="0"/>
@@ -11442,7 +11442,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M181" s="0"/>
       <c r="N181" s="0"/>
@@ -11485,7 +11485,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M182" s="0"/>
       <c r="N182" s="0"/>
@@ -11528,7 +11528,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M183" s="0"/>
       <c r="N183" s="0"/>
@@ -11571,7 +11571,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M184" s="0"/>
       <c r="N184" s="0"/>
@@ -11614,7 +11614,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M185" s="0"/>
       <c r="N185" s="0"/>
@@ -11657,7 +11657,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M186" s="0"/>
       <c r="N186" s="0"/>
@@ -11700,7 +11700,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M187" s="0"/>
       <c r="N187" s="0"/>
@@ -11743,7 +11743,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M188" s="0"/>
       <c r="N188" s="0"/>
@@ -11786,7 +11786,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M189" s="0"/>
       <c r="N189" s="0"/>
@@ -11829,7 +11829,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M190" s="0"/>
       <c r="N190" s="0"/>
@@ -11872,7 +11872,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M191" s="0"/>
       <c r="N191" s="0"/>
@@ -11915,7 +11915,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M192" s="0"/>
       <c r="N192" s="0"/>
@@ -11958,7 +11958,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M193" s="0"/>
       <c r="N193" s="0"/>
@@ -12001,7 +12001,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M194" s="0"/>
       <c r="N194" s="0"/>
@@ -12044,7 +12044,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M195" s="0"/>
       <c r="N195" s="0"/>
@@ -12087,7 +12087,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M196" s="0"/>
       <c r="N196" s="0"/>
@@ -12130,7 +12130,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M197" s="0"/>
       <c r="N197" s="0"/>
@@ -12173,7 +12173,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M198" s="0"/>
       <c r="N198" s="0"/>
@@ -12216,7 +12216,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M199" s="0"/>
       <c r="N199" s="0"/>
@@ -12259,7 +12259,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M200" s="0"/>
       <c r="N200" s="0"/>
@@ -12302,7 +12302,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M201" s="0"/>
       <c r="N201" s="0"/>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -9350,7 +9350,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M139" s="0"/>
       <c r="N139" s="0"/>
@@ -9393,7 +9393,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M140" s="0"/>
       <c r="N140" s="0"/>
@@ -9436,7 +9436,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M141" s="0"/>
       <c r="N141" s="0"/>
@@ -9479,7 +9479,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M142" s="0"/>
       <c r="N142" s="0"/>
@@ -9522,7 +9522,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M143" s="0"/>
       <c r="N143" s="0"/>
@@ -9695,7 +9695,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M146" s="0"/>
       <c r="N146" s="0"/>
@@ -9803,7 +9803,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M148" s="0"/>
       <c r="N148" s="0"/>
@@ -10171,7 +10171,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M154" s="0"/>
       <c r="N154" s="0"/>
@@ -10279,7 +10279,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M156" s="0"/>
       <c r="N156" s="0"/>
@@ -10452,7 +10452,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M159" s="0"/>
       <c r="N159" s="0"/>
@@ -10625,7 +10625,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M162" s="0"/>
       <c r="N162" s="0"/>
@@ -10668,7 +10668,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M163" s="0"/>
       <c r="N163" s="0"/>
@@ -10711,7 +10711,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M164" s="0"/>
       <c r="N164" s="0"/>
@@ -10754,7 +10754,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M165" s="0"/>
       <c r="N165" s="0"/>
@@ -10797,7 +10797,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M166" s="0"/>
       <c r="N166" s="0"/>
@@ -10840,7 +10840,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M167" s="0"/>
       <c r="N167" s="0"/>
@@ -10883,7 +10883,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M168" s="0"/>
       <c r="N168" s="0"/>
@@ -10926,7 +10926,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M169" s="0"/>
       <c r="N169" s="0"/>
@@ -10969,7 +10969,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M170" s="0"/>
       <c r="N170" s="0"/>
@@ -11012,7 +11012,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M171" s="0"/>
       <c r="N171" s="0"/>
@@ -11055,7 +11055,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M172" s="0"/>
       <c r="N172" s="0"/>
@@ -11098,7 +11098,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M173" s="0"/>
       <c r="N173" s="0"/>
@@ -11141,7 +11141,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M174" s="0"/>
       <c r="N174" s="0"/>
@@ -11184,7 +11184,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M175" s="0"/>
       <c r="N175" s="0"/>
@@ -11227,7 +11227,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M176" s="0"/>
       <c r="N176" s="0"/>
@@ -11270,7 +11270,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M177" s="0"/>
       <c r="N177" s="0"/>
@@ -11313,7 +11313,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M178" s="0"/>
       <c r="N178" s="0"/>
@@ -11356,7 +11356,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M179" s="0"/>
       <c r="N179" s="0"/>
@@ -11399,7 +11399,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M180" s="0"/>
       <c r="N180" s="0"/>
@@ -11442,7 +11442,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M181" s="0"/>
       <c r="N181" s="0"/>
@@ -11485,7 +11485,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M182" s="0"/>
       <c r="N182" s="0"/>
@@ -11528,7 +11528,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M183" s="0"/>
       <c r="N183" s="0"/>
@@ -11571,7 +11571,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M184" s="0"/>
       <c r="N184" s="0"/>
@@ -11614,7 +11614,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M185" s="0"/>
       <c r="N185" s="0"/>
@@ -11657,7 +11657,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M186" s="0"/>
       <c r="N186" s="0"/>
@@ -11700,7 +11700,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M187" s="0"/>
       <c r="N187" s="0"/>
@@ -11743,7 +11743,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M188" s="0"/>
       <c r="N188" s="0"/>
@@ -11786,7 +11786,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M189" s="0"/>
       <c r="N189" s="0"/>
@@ -11829,7 +11829,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M190" s="0"/>
       <c r="N190" s="0"/>
@@ -11872,7 +11872,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M191" s="0"/>
       <c r="N191" s="0"/>
@@ -11915,7 +11915,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M192" s="0"/>
       <c r="N192" s="0"/>
@@ -11958,7 +11958,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M193" s="0"/>
       <c r="N193" s="0"/>
@@ -12001,7 +12001,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M194" s="0"/>
       <c r="N194" s="0"/>
@@ -12044,7 +12044,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M195" s="0"/>
       <c r="N195" s="0"/>
@@ -12087,7 +12087,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M196" s="0"/>
       <c r="N196" s="0"/>
@@ -12130,7 +12130,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M197" s="0"/>
       <c r="N197" s="0"/>
@@ -12173,7 +12173,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M198" s="0"/>
       <c r="N198" s="0"/>
@@ -12216,7 +12216,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M199" s="0"/>
       <c r="N199" s="0"/>
@@ -12259,7 +12259,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M200" s="0"/>
       <c r="N200" s="0"/>
@@ -12302,7 +12302,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M201" s="0"/>
       <c r="N201" s="0"/>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -9350,7 +9350,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M139" s="0"/>
       <c r="N139" s="0"/>
@@ -9393,7 +9393,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M140" s="0"/>
       <c r="N140" s="0"/>
@@ -9436,7 +9436,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M141" s="0"/>
       <c r="N141" s="0"/>
@@ -9479,7 +9479,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M142" s="0"/>
       <c r="N142" s="0"/>
@@ -9522,7 +9522,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M143" s="0"/>
       <c r="N143" s="0"/>
@@ -9695,7 +9695,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M146" s="0"/>
       <c r="N146" s="0"/>
@@ -9803,7 +9803,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M148" s="0"/>
       <c r="N148" s="0"/>
@@ -10171,7 +10171,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M154" s="0"/>
       <c r="N154" s="0"/>
@@ -10279,7 +10279,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M156" s="0"/>
       <c r="N156" s="0"/>
@@ -10452,7 +10452,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M159" s="0"/>
       <c r="N159" s="0"/>
@@ -10625,7 +10625,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M162" s="0"/>
       <c r="N162" s="0"/>
@@ -10668,7 +10668,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M163" s="0"/>
       <c r="N163" s="0"/>
@@ -10711,7 +10711,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M164" s="0"/>
       <c r="N164" s="0"/>
@@ -10754,7 +10754,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M165" s="0"/>
       <c r="N165" s="0"/>
@@ -10797,7 +10797,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M166" s="0"/>
       <c r="N166" s="0"/>
@@ -10840,7 +10840,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M167" s="0"/>
       <c r="N167" s="0"/>
@@ -10883,7 +10883,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M168" s="0"/>
       <c r="N168" s="0"/>
@@ -10926,7 +10926,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M169" s="0"/>
       <c r="N169" s="0"/>
@@ -10969,7 +10969,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M170" s="0"/>
       <c r="N170" s="0"/>
@@ -11012,7 +11012,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M171" s="0"/>
       <c r="N171" s="0"/>
@@ -11055,7 +11055,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M172" s="0"/>
       <c r="N172" s="0"/>
@@ -11098,7 +11098,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M173" s="0"/>
       <c r="N173" s="0"/>
@@ -11141,7 +11141,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M174" s="0"/>
       <c r="N174" s="0"/>
@@ -11184,7 +11184,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M175" s="0"/>
       <c r="N175" s="0"/>
@@ -11227,7 +11227,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M176" s="0"/>
       <c r="N176" s="0"/>
@@ -11270,7 +11270,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M177" s="0"/>
       <c r="N177" s="0"/>
@@ -11313,7 +11313,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M178" s="0"/>
       <c r="N178" s="0"/>
@@ -11356,7 +11356,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M179" s="0"/>
       <c r="N179" s="0"/>
@@ -11399,7 +11399,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M180" s="0"/>
       <c r="N180" s="0"/>
@@ -11442,7 +11442,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M181" s="0"/>
       <c r="N181" s="0"/>
@@ -11485,7 +11485,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M182" s="0"/>
       <c r="N182" s="0"/>
@@ -11528,7 +11528,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M183" s="0"/>
       <c r="N183" s="0"/>
@@ -11571,7 +11571,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M184" s="0"/>
       <c r="N184" s="0"/>
@@ -11614,7 +11614,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M185" s="0"/>
       <c r="N185" s="0"/>
@@ -11657,7 +11657,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M186" s="0"/>
       <c r="N186" s="0"/>
@@ -11700,7 +11700,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M187" s="0"/>
       <c r="N187" s="0"/>
@@ -11743,7 +11743,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M188" s="0"/>
       <c r="N188" s="0"/>
@@ -11786,7 +11786,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M189" s="0"/>
       <c r="N189" s="0"/>
@@ -11829,7 +11829,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M190" s="0"/>
       <c r="N190" s="0"/>
@@ -11872,7 +11872,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M191" s="0"/>
       <c r="N191" s="0"/>
@@ -11915,7 +11915,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M192" s="0"/>
       <c r="N192" s="0"/>
@@ -11958,7 +11958,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M193" s="0"/>
       <c r="N193" s="0"/>
@@ -12001,7 +12001,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M194" s="0"/>
       <c r="N194" s="0"/>
@@ -12044,7 +12044,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M195" s="0"/>
       <c r="N195" s="0"/>
@@ -12087,7 +12087,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M196" s="0"/>
       <c r="N196" s="0"/>
@@ -12130,7 +12130,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M197" s="0"/>
       <c r="N197" s="0"/>
@@ -12173,7 +12173,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M198" s="0"/>
       <c r="N198" s="0"/>
@@ -12216,7 +12216,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M199" s="0"/>
       <c r="N199" s="0"/>
@@ -12259,7 +12259,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M200" s="0"/>
       <c r="N200" s="0"/>
@@ -12302,7 +12302,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M201" s="0"/>
       <c r="N201" s="0"/>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -9350,7 +9350,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M139" s="0"/>
       <c r="N139" s="0"/>
@@ -9393,7 +9393,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M140" s="0"/>
       <c r="N140" s="0"/>
@@ -9436,7 +9436,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M141" s="0"/>
       <c r="N141" s="0"/>
@@ -9479,7 +9479,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M142" s="0"/>
       <c r="N142" s="0"/>
@@ -9522,7 +9522,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M143" s="0"/>
       <c r="N143" s="0"/>
@@ -9695,7 +9695,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M146" s="0"/>
       <c r="N146" s="0"/>
@@ -9803,7 +9803,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M148" s="0"/>
       <c r="N148" s="0"/>
@@ -10171,7 +10171,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M154" s="0"/>
       <c r="N154" s="0"/>
@@ -10279,7 +10279,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M156" s="0"/>
       <c r="N156" s="0"/>
@@ -10452,7 +10452,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M159" s="0"/>
       <c r="N159" s="0"/>
@@ -10625,7 +10625,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M162" s="0"/>
       <c r="N162" s="0"/>
@@ -10668,7 +10668,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M163" s="0"/>
       <c r="N163" s="0"/>
@@ -10711,7 +10711,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M164" s="0"/>
       <c r="N164" s="0"/>
@@ -10754,7 +10754,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M165" s="0"/>
       <c r="N165" s="0"/>
@@ -10797,7 +10797,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M166" s="0"/>
       <c r="N166" s="0"/>
@@ -10840,7 +10840,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M167" s="0"/>
       <c r="N167" s="0"/>
@@ -10883,7 +10883,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M168" s="0"/>
       <c r="N168" s="0"/>
@@ -10926,7 +10926,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M169" s="0"/>
       <c r="N169" s="0"/>
@@ -10969,7 +10969,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M170" s="0"/>
       <c r="N170" s="0"/>
@@ -11012,7 +11012,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M171" s="0"/>
       <c r="N171" s="0"/>
@@ -11055,7 +11055,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M172" s="0"/>
       <c r="N172" s="0"/>
@@ -11098,7 +11098,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M173" s="0"/>
       <c r="N173" s="0"/>
@@ -11141,7 +11141,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M174" s="0"/>
       <c r="N174" s="0"/>
@@ -11184,7 +11184,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M175" s="0"/>
       <c r="N175" s="0"/>
@@ -11227,7 +11227,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M176" s="0"/>
       <c r="N176" s="0"/>
@@ -11270,7 +11270,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M177" s="0"/>
       <c r="N177" s="0"/>
@@ -11313,7 +11313,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M178" s="0"/>
       <c r="N178" s="0"/>
@@ -11356,7 +11356,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M179" s="0"/>
       <c r="N179" s="0"/>
@@ -11399,7 +11399,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M180" s="0"/>
       <c r="N180" s="0"/>
@@ -11442,7 +11442,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M181" s="0"/>
       <c r="N181" s="0"/>
@@ -11485,7 +11485,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M182" s="0"/>
       <c r="N182" s="0"/>
@@ -11528,7 +11528,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M183" s="0"/>
       <c r="N183" s="0"/>
@@ -11571,7 +11571,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M184" s="0"/>
       <c r="N184" s="0"/>
@@ -11614,7 +11614,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M185" s="0"/>
       <c r="N185" s="0"/>
@@ -11657,7 +11657,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M186" s="0"/>
       <c r="N186" s="0"/>
@@ -11700,7 +11700,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M187" s="0"/>
       <c r="N187" s="0"/>
@@ -11743,7 +11743,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M188" s="0"/>
       <c r="N188" s="0"/>
@@ -11786,7 +11786,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M189" s="0"/>
       <c r="N189" s="0"/>
@@ -11829,7 +11829,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M190" s="0"/>
       <c r="N190" s="0"/>
@@ -11872,7 +11872,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M191" s="0"/>
       <c r="N191" s="0"/>
@@ -11915,7 +11915,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M192" s="0"/>
       <c r="N192" s="0"/>
@@ -11958,7 +11958,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M193" s="0"/>
       <c r="N193" s="0"/>
@@ -12001,7 +12001,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M194" s="0"/>
       <c r="N194" s="0"/>
@@ -12044,7 +12044,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M195" s="0"/>
       <c r="N195" s="0"/>
@@ -12087,7 +12087,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M196" s="0"/>
       <c r="N196" s="0"/>
@@ -12130,7 +12130,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M197" s="0"/>
       <c r="N197" s="0"/>
@@ -12173,7 +12173,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M198" s="0"/>
       <c r="N198" s="0"/>
@@ -12216,7 +12216,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M199" s="0"/>
       <c r="N199" s="0"/>
@@ -12259,7 +12259,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M200" s="0"/>
       <c r="N200" s="0"/>
@@ -12302,7 +12302,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M201" s="0"/>
       <c r="N201" s="0"/>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -9350,7 +9350,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M139" s="0"/>
       <c r="N139" s="0"/>
@@ -9393,7 +9393,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M140" s="0"/>
       <c r="N140" s="0"/>
@@ -9436,7 +9436,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M141" s="0"/>
       <c r="N141" s="0"/>
@@ -9479,7 +9479,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M142" s="0"/>
       <c r="N142" s="0"/>
@@ -9522,7 +9522,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M143" s="0"/>
       <c r="N143" s="0"/>
@@ -9695,7 +9695,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M146" s="0"/>
       <c r="N146" s="0"/>
@@ -9803,7 +9803,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M148" s="0"/>
       <c r="N148" s="0"/>
@@ -10171,7 +10171,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M154" s="0"/>
       <c r="N154" s="0"/>
@@ -10279,7 +10279,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M156" s="0"/>
       <c r="N156" s="0"/>
@@ -10452,7 +10452,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M159" s="0"/>
       <c r="N159" s="0"/>
@@ -10625,7 +10625,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M162" s="0"/>
       <c r="N162" s="0"/>
@@ -10668,7 +10668,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M163" s="0"/>
       <c r="N163" s="0"/>
@@ -10711,7 +10711,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M164" s="0"/>
       <c r="N164" s="0"/>
@@ -10754,7 +10754,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M165" s="0"/>
       <c r="N165" s="0"/>
@@ -10797,7 +10797,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M166" s="0"/>
       <c r="N166" s="0"/>
@@ -10840,7 +10840,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M167" s="0"/>
       <c r="N167" s="0"/>
@@ -10883,7 +10883,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M168" s="0"/>
       <c r="N168" s="0"/>
@@ -10926,7 +10926,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M169" s="0"/>
       <c r="N169" s="0"/>
@@ -10969,7 +10969,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M170" s="0"/>
       <c r="N170" s="0"/>
@@ -11012,7 +11012,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M171" s="0"/>
       <c r="N171" s="0"/>
@@ -11055,7 +11055,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M172" s="0"/>
       <c r="N172" s="0"/>
@@ -11098,7 +11098,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M173" s="0"/>
       <c r="N173" s="0"/>
@@ -11141,7 +11141,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M174" s="0"/>
       <c r="N174" s="0"/>
@@ -11184,7 +11184,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M175" s="0"/>
       <c r="N175" s="0"/>
@@ -11227,7 +11227,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M176" s="0"/>
       <c r="N176" s="0"/>
@@ -11270,7 +11270,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M177" s="0"/>
       <c r="N177" s="0"/>
@@ -11313,7 +11313,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M178" s="0"/>
       <c r="N178" s="0"/>
@@ -11356,7 +11356,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M179" s="0"/>
       <c r="N179" s="0"/>
@@ -11399,7 +11399,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M180" s="0"/>
       <c r="N180" s="0"/>
@@ -11442,7 +11442,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M181" s="0"/>
       <c r="N181" s="0"/>
@@ -11485,7 +11485,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M182" s="0"/>
       <c r="N182" s="0"/>
@@ -11528,7 +11528,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M183" s="0"/>
       <c r="N183" s="0"/>
@@ -11571,7 +11571,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M184" s="0"/>
       <c r="N184" s="0"/>
@@ -11614,7 +11614,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M185" s="0"/>
       <c r="N185" s="0"/>
@@ -11657,7 +11657,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M186" s="0"/>
       <c r="N186" s="0"/>
@@ -11700,7 +11700,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M187" s="0"/>
       <c r="N187" s="0"/>
@@ -11743,7 +11743,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M188" s="0"/>
       <c r="N188" s="0"/>
@@ -11786,7 +11786,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M189" s="0"/>
       <c r="N189" s="0"/>
@@ -11829,7 +11829,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M190" s="0"/>
       <c r="N190" s="0"/>
@@ -11872,7 +11872,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M191" s="0"/>
       <c r="N191" s="0"/>
@@ -11915,7 +11915,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M192" s="0"/>
       <c r="N192" s="0"/>
@@ -11958,7 +11958,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M193" s="0"/>
       <c r="N193" s="0"/>
@@ -12001,7 +12001,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M194" s="0"/>
       <c r="N194" s="0"/>
@@ -12044,7 +12044,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M195" s="0"/>
       <c r="N195" s="0"/>
@@ -12087,7 +12087,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M196" s="0"/>
       <c r="N196" s="0"/>
@@ -12130,7 +12130,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M197" s="0"/>
       <c r="N197" s="0"/>
@@ -12173,7 +12173,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M198" s="0"/>
       <c r="N198" s="0"/>
@@ -12216,7 +12216,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M199" s="0"/>
       <c r="N199" s="0"/>
@@ -12259,7 +12259,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M200" s="0"/>
       <c r="N200" s="0"/>
@@ -12302,7 +12302,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M201" s="0"/>
       <c r="N201" s="0"/>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -9350,7 +9350,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M139" s="0"/>
       <c r="N139" s="0"/>
@@ -9393,7 +9393,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M140" s="0"/>
       <c r="N140" s="0"/>
@@ -9436,7 +9436,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M141" s="0"/>
       <c r="N141" s="0"/>
@@ -9479,7 +9479,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M142" s="0"/>
       <c r="N142" s="0"/>
@@ -9522,7 +9522,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M143" s="0"/>
       <c r="N143" s="0"/>
@@ -9695,7 +9695,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M146" s="0"/>
       <c r="N146" s="0"/>
@@ -9803,7 +9803,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M148" s="0"/>
       <c r="N148" s="0"/>
@@ -10171,7 +10171,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M154" s="0"/>
       <c r="N154" s="0"/>
@@ -10279,7 +10279,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M156" s="0"/>
       <c r="N156" s="0"/>
@@ -10452,7 +10452,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M159" s="0"/>
       <c r="N159" s="0"/>
@@ -10625,7 +10625,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M162" s="0"/>
       <c r="N162" s="0"/>
@@ -10668,7 +10668,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M163" s="0"/>
       <c r="N163" s="0"/>
@@ -10711,7 +10711,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M164" s="0"/>
       <c r="N164" s="0"/>
@@ -10754,7 +10754,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M165" s="0"/>
       <c r="N165" s="0"/>
@@ -10797,7 +10797,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M166" s="0"/>
       <c r="N166" s="0"/>
@@ -10840,7 +10840,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M167" s="0"/>
       <c r="N167" s="0"/>
@@ -10883,7 +10883,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M168" s="0"/>
       <c r="N168" s="0"/>
@@ -10926,7 +10926,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M169" s="0"/>
       <c r="N169" s="0"/>
@@ -10969,7 +10969,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M170" s="0"/>
       <c r="N170" s="0"/>
@@ -11012,7 +11012,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M171" s="0"/>
       <c r="N171" s="0"/>
@@ -11055,7 +11055,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M172" s="0"/>
       <c r="N172" s="0"/>
@@ -11098,7 +11098,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M173" s="0"/>
       <c r="N173" s="0"/>
@@ -11141,7 +11141,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M174" s="0"/>
       <c r="N174" s="0"/>
@@ -11184,7 +11184,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M175" s="0"/>
       <c r="N175" s="0"/>
@@ -11227,7 +11227,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M176" s="0"/>
       <c r="N176" s="0"/>
@@ -11270,7 +11270,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M177" s="0"/>
       <c r="N177" s="0"/>
@@ -11313,7 +11313,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M178" s="0"/>
       <c r="N178" s="0"/>
@@ -11356,7 +11356,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M179" s="0"/>
       <c r="N179" s="0"/>
@@ -11399,7 +11399,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M180" s="0"/>
       <c r="N180" s="0"/>
@@ -11442,7 +11442,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M181" s="0"/>
       <c r="N181" s="0"/>
@@ -11485,7 +11485,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M182" s="0"/>
       <c r="N182" s="0"/>
@@ -11528,7 +11528,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M183" s="0"/>
       <c r="N183" s="0"/>
@@ -11571,7 +11571,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M184" s="0"/>
       <c r="N184" s="0"/>
@@ -11614,7 +11614,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M185" s="0"/>
       <c r="N185" s="0"/>
@@ -11657,7 +11657,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M186" s="0"/>
       <c r="N186" s="0"/>
@@ -11700,7 +11700,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M187" s="0"/>
       <c r="N187" s="0"/>
@@ -11743,7 +11743,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M188" s="0"/>
       <c r="N188" s="0"/>
@@ -11786,7 +11786,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M189" s="0"/>
       <c r="N189" s="0"/>
@@ -11829,7 +11829,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M190" s="0"/>
       <c r="N190" s="0"/>
@@ -11872,7 +11872,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M191" s="0"/>
       <c r="N191" s="0"/>
@@ -11915,7 +11915,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M192" s="0"/>
       <c r="N192" s="0"/>
@@ -11958,7 +11958,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M193" s="0"/>
       <c r="N193" s="0"/>
@@ -12001,7 +12001,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M194" s="0"/>
       <c r="N194" s="0"/>
@@ -12044,7 +12044,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M195" s="0"/>
       <c r="N195" s="0"/>
@@ -12087,7 +12087,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M196" s="0"/>
       <c r="N196" s="0"/>
@@ -12130,7 +12130,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M197" s="0"/>
       <c r="N197" s="0"/>
@@ -12173,7 +12173,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M198" s="0"/>
       <c r="N198" s="0"/>
@@ -12216,7 +12216,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M199" s="0"/>
       <c r="N199" s="0"/>
@@ -12259,7 +12259,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M200" s="0"/>
       <c r="N200" s="0"/>
@@ -12302,7 +12302,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M201" s="0"/>
       <c r="N201" s="0"/>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -301,7 +301,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:R201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="12.100000000000001" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -316,11 +316,12 @@
     <col width="7.700000000000001" min="10" max="10" bestFit="1" customWidth="1"/>
     <col width="22.0" min="11" max="11" bestFit="1" customWidth="1"/>
     <col width="23.1" min="12" max="12" bestFit="1" customWidth="1"/>
-    <col width="16.5" min="13" max="13" bestFit="1" customWidth="1"/>
-    <col width="17.6" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="99.00000000000001" min="13" max="13" bestFit="1" customWidth="1"/>
+    <col width="16.5" min="14" max="14" bestFit="1" customWidth="1"/>
+    <col width="17.6" min="15" max="15" bestFit="1" customWidth="1"/>
     <col width="18.700000000000003" min="16" max="16" bestFit="1" customWidth="1"/>
     <col width="18.700000000000003" min="17" max="17" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="18" max="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -386,25 +387,30 @@
       </c>
       <c r="M1" s="0" t="inlineStr">
         <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="N1" s="0" t="inlineStr">
+        <is>
           <t>Done ≤ 1 day</t>
         </is>
       </c>
-      <c r="N1" s="0" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 7 days</t>
         </is>
       </c>
-      <c r="O1" s="0" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 14 days</t>
         </is>
       </c>
-      <c r="P1" s="0" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 21 days</t>
         </is>
       </c>
-      <c r="Q1" s="0" t="inlineStr">
+      <c r="R1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 28 days</t>
         </is>
@@ -459,11 +465,13 @@
         <v>6</v>
       </c>
       <c r="L2" s="0"/>
-      <c r="M2" s="0" t="b">
-        <v>0</v>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N2" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="0" t="b">
         <v>1</v>
@@ -472,6 +480,9 @@
         <v>1</v>
       </c>
       <c r="Q2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -524,19 +535,24 @@
         <v>12</v>
       </c>
       <c r="L3" s="0"/>
-      <c r="M3" s="0" t="b">
-        <v>0</v>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N3" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O3" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -589,8 +605,10 @@
         <v>16</v>
       </c>
       <c r="L4" s="0"/>
-      <c r="M4" s="0" t="b">
-        <v>0</v>
+      <c r="M4" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N4" s="0" t="b">
         <v>0</v>
@@ -599,9 +617,12 @@
         <v>0</v>
       </c>
       <c r="P4" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -654,8 +675,10 @@
         <v>16</v>
       </c>
       <c r="L5" s="0"/>
-      <c r="M5" s="0" t="b">
-        <v>0</v>
+      <c r="M5" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N5" s="0" t="b">
         <v>0</v>
@@ -664,9 +687,12 @@
         <v>0</v>
       </c>
       <c r="P5" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -719,19 +745,24 @@
         <v>11</v>
       </c>
       <c r="L6" s="0"/>
-      <c r="M6" s="0" t="b">
-        <v>0</v>
+      <c r="M6" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N6" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O6" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -784,19 +815,24 @@
         <v>12</v>
       </c>
       <c r="L7" s="0"/>
-      <c r="M7" s="0" t="b">
-        <v>0</v>
+      <c r="M7" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N7" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -849,11 +885,13 @@
         <v>6</v>
       </c>
       <c r="L8" s="0"/>
-      <c r="M8" s="0" t="b">
-        <v>0</v>
+      <c r="M8" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N8" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="0" t="b">
         <v>1</v>
@@ -862,6 +900,9 @@
         <v>1</v>
       </c>
       <c r="Q8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -914,11 +955,13 @@
         <v>6</v>
       </c>
       <c r="L9" s="0"/>
-      <c r="M9" s="0" t="b">
-        <v>0</v>
+      <c r="M9" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N9" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="0" t="b">
         <v>1</v>
@@ -927,6 +970,9 @@
         <v>1</v>
       </c>
       <c r="Q9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -979,19 +1025,24 @@
         <v>9</v>
       </c>
       <c r="L10" s="0"/>
-      <c r="M10" s="0" t="b">
-        <v>0</v>
+      <c r="M10" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N10" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O10" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1044,8 +1095,10 @@
         <v>19</v>
       </c>
       <c r="L11" s="0"/>
-      <c r="M11" s="0" t="b">
-        <v>0</v>
+      <c r="M11" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N11" s="0" t="b">
         <v>0</v>
@@ -1054,9 +1107,12 @@
         <v>0</v>
       </c>
       <c r="P11" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1109,8 +1165,10 @@
         <v>20</v>
       </c>
       <c r="L12" s="0"/>
-      <c r="M12" s="0" t="b">
-        <v>0</v>
+      <c r="M12" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N12" s="0" t="b">
         <v>0</v>
@@ -1119,9 +1177,12 @@
         <v>0</v>
       </c>
       <c r="P12" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1174,11 +1235,13 @@
         <v>3</v>
       </c>
       <c r="L13" s="0"/>
-      <c r="M13" s="0" t="b">
-        <v>0</v>
+      <c r="M13" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N13" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="0" t="b">
         <v>1</v>
@@ -1187,6 +1250,9 @@
         <v>1</v>
       </c>
       <c r="Q13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1239,8 +1305,10 @@
         <v>15</v>
       </c>
       <c r="L14" s="0"/>
-      <c r="M14" s="0" t="b">
-        <v>0</v>
+      <c r="M14" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N14" s="0" t="b">
         <v>0</v>
@@ -1249,9 +1317,12 @@
         <v>0</v>
       </c>
       <c r="P14" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1304,11 +1375,13 @@
         <v>6</v>
       </c>
       <c r="L15" s="0"/>
-      <c r="M15" s="0" t="b">
-        <v>0</v>
+      <c r="M15" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N15" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="0" t="b">
         <v>1</v>
@@ -1317,6 +1390,9 @@
         <v>1</v>
       </c>
       <c r="Q15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1369,8 +1445,10 @@
         <v>20</v>
       </c>
       <c r="L16" s="0"/>
-      <c r="M16" s="0" t="b">
-        <v>0</v>
+      <c r="M16" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N16" s="0" t="b">
         <v>0</v>
@@ -1379,9 +1457,12 @@
         <v>0</v>
       </c>
       <c r="P16" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1434,8 +1515,10 @@
         <v>18</v>
       </c>
       <c r="L17" s="0"/>
-      <c r="M17" s="0" t="b">
-        <v>0</v>
+      <c r="M17" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N17" s="0" t="b">
         <v>0</v>
@@ -1444,9 +1527,12 @@
         <v>0</v>
       </c>
       <c r="P17" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1499,19 +1585,24 @@
         <v>9</v>
       </c>
       <c r="L18" s="0"/>
-      <c r="M18" s="0" t="b">
-        <v>0</v>
+      <c r="M18" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N18" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O18" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1564,19 +1655,24 @@
         <v>11</v>
       </c>
       <c r="L19" s="0"/>
-      <c r="M19" s="0" t="b">
-        <v>0</v>
+      <c r="M19" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N19" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O19" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1629,11 +1725,13 @@
         <v>5</v>
       </c>
       <c r="L20" s="0"/>
-      <c r="M20" s="0" t="b">
-        <v>0</v>
+      <c r="M20" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N20" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="0" t="b">
         <v>1</v>
@@ -1642,6 +1740,9 @@
         <v>1</v>
       </c>
       <c r="Q20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1694,11 +1795,13 @@
         <v>5</v>
       </c>
       <c r="L21" s="0"/>
-      <c r="M21" s="0" t="b">
-        <v>0</v>
+      <c r="M21" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N21" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" s="0" t="b">
         <v>1</v>
@@ -1707,6 +1810,9 @@
         <v>1</v>
       </c>
       <c r="Q21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1759,8 +1865,10 @@
         <v>19</v>
       </c>
       <c r="L22" s="0"/>
-      <c r="M22" s="0" t="b">
-        <v>0</v>
+      <c r="M22" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N22" s="0" t="b">
         <v>0</v>
@@ -1769,9 +1877,12 @@
         <v>0</v>
       </c>
       <c r="P22" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1824,11 +1935,13 @@
         <v>3</v>
       </c>
       <c r="L23" s="0"/>
-      <c r="M23" s="0" t="b">
-        <v>0</v>
+      <c r="M23" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N23" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="0" t="b">
         <v>1</v>
@@ -1837,6 +1950,9 @@
         <v>1</v>
       </c>
       <c r="Q23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1889,8 +2005,10 @@
         <v>21</v>
       </c>
       <c r="L24" s="0"/>
-      <c r="M24" s="0" t="b">
-        <v>0</v>
+      <c r="M24" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N24" s="0" t="b">
         <v>0</v>
@@ -1899,9 +2017,12 @@
         <v>0</v>
       </c>
       <c r="P24" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1954,8 +2075,10 @@
         <v>17</v>
       </c>
       <c r="L25" s="0"/>
-      <c r="M25" s="0" t="b">
-        <v>0</v>
+      <c r="M25" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N25" s="0" t="b">
         <v>0</v>
@@ -1964,9 +2087,12 @@
         <v>0</v>
       </c>
       <c r="P25" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2019,19 +2145,24 @@
         <v>12</v>
       </c>
       <c r="L26" s="0"/>
-      <c r="M26" s="0" t="b">
-        <v>0</v>
+      <c r="M26" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N26" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O26" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q26" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2084,19 +2215,24 @@
         <v>14</v>
       </c>
       <c r="L27" s="0"/>
-      <c r="M27" s="0" t="b">
-        <v>0</v>
+      <c r="M27" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N27" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O27" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2149,11 +2285,13 @@
         <v>7</v>
       </c>
       <c r="L28" s="0"/>
-      <c r="M28" s="0" t="b">
-        <v>0</v>
+      <c r="M28" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N28" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="0" t="b">
         <v>1</v>
@@ -2162,6 +2300,9 @@
         <v>1</v>
       </c>
       <c r="Q28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2214,11 +2355,13 @@
         <v>7</v>
       </c>
       <c r="L29" s="0"/>
-      <c r="M29" s="0" t="b">
-        <v>0</v>
+      <c r="M29" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N29" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" s="0" t="b">
         <v>1</v>
@@ -2227,6 +2370,9 @@
         <v>1</v>
       </c>
       <c r="Q29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2279,11 +2425,13 @@
         <v>7</v>
       </c>
       <c r="L30" s="0"/>
-      <c r="M30" s="0" t="b">
-        <v>0</v>
+      <c r="M30" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N30" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" s="0" t="b">
         <v>1</v>
@@ -2292,6 +2440,9 @@
         <v>1</v>
       </c>
       <c r="Q30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2344,11 +2495,13 @@
         <v>4</v>
       </c>
       <c r="L31" s="0"/>
-      <c r="M31" s="0" t="b">
-        <v>0</v>
+      <c r="M31" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N31" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="0" t="b">
         <v>1</v>
@@ -2357,6 +2510,9 @@
         <v>1</v>
       </c>
       <c r="Q31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2409,19 +2565,24 @@
         <v>9</v>
       </c>
       <c r="L32" s="0"/>
-      <c r="M32" s="0" t="b">
-        <v>0</v>
+      <c r="M32" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N32" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O32" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q32" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2474,11 +2635,13 @@
         <v>6</v>
       </c>
       <c r="L33" s="0"/>
-      <c r="M33" s="0" t="b">
-        <v>0</v>
+      <c r="M33" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N33" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="0" t="b">
         <v>1</v>
@@ -2487,6 +2650,9 @@
         <v>1</v>
       </c>
       <c r="Q33" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2539,19 +2705,24 @@
         <v>13</v>
       </c>
       <c r="L34" s="0"/>
-      <c r="M34" s="0" t="b">
-        <v>0</v>
+      <c r="M34" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N34" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O34" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q34" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2604,19 +2775,24 @@
         <v>9</v>
       </c>
       <c r="L35" s="0"/>
-      <c r="M35" s="0" t="b">
-        <v>0</v>
+      <c r="M35" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N35" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O35" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q35" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2669,8 +2845,10 @@
         <v>19</v>
       </c>
       <c r="L36" s="0"/>
-      <c r="M36" s="0" t="b">
-        <v>0</v>
+      <c r="M36" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N36" s="0" t="b">
         <v>0</v>
@@ -2679,9 +2857,12 @@
         <v>0</v>
       </c>
       <c r="P36" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2734,8 +2915,10 @@
         <v>21</v>
       </c>
       <c r="L37" s="0"/>
-      <c r="M37" s="0" t="b">
-        <v>0</v>
+      <c r="M37" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N37" s="0" t="b">
         <v>0</v>
@@ -2744,9 +2927,12 @@
         <v>0</v>
       </c>
       <c r="P37" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2799,8 +2985,10 @@
         <v>17</v>
       </c>
       <c r="L38" s="0"/>
-      <c r="M38" s="0" t="b">
-        <v>0</v>
+      <c r="M38" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N38" s="0" t="b">
         <v>0</v>
@@ -2809,9 +2997,12 @@
         <v>0</v>
       </c>
       <c r="P38" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2864,11 +3055,13 @@
         <v>3</v>
       </c>
       <c r="L39" s="0"/>
-      <c r="M39" s="0" t="b">
-        <v>0</v>
+      <c r="M39" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N39" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" s="0" t="b">
         <v>1</v>
@@ -2877,6 +3070,9 @@
         <v>1</v>
       </c>
       <c r="Q39" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2929,8 +3125,10 @@
         <v>16</v>
       </c>
       <c r="L40" s="0"/>
-      <c r="M40" s="0" t="b">
-        <v>0</v>
+      <c r="M40" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N40" s="0" t="b">
         <v>0</v>
@@ -2939,9 +3137,12 @@
         <v>0</v>
       </c>
       <c r="P40" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2994,8 +3195,10 @@
         <v>16</v>
       </c>
       <c r="L41" s="0"/>
-      <c r="M41" s="0" t="b">
-        <v>0</v>
+      <c r="M41" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N41" s="0" t="b">
         <v>0</v>
@@ -3004,9 +3207,12 @@
         <v>0</v>
       </c>
       <c r="P41" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q41" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3059,11 +3265,13 @@
         <v>2</v>
       </c>
       <c r="L42" s="0"/>
-      <c r="M42" s="0" t="b">
-        <v>0</v>
+      <c r="M42" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N42" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="0" t="b">
         <v>1</v>
@@ -3072,6 +3280,9 @@
         <v>1</v>
       </c>
       <c r="Q42" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R42" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3124,8 +3335,10 @@
         <v>18</v>
       </c>
       <c r="L43" s="0"/>
-      <c r="M43" s="0" t="b">
-        <v>0</v>
+      <c r="M43" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N43" s="0" t="b">
         <v>0</v>
@@ -3134,9 +3347,12 @@
         <v>0</v>
       </c>
       <c r="P43" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R43" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3189,11 +3405,13 @@
         <v>6</v>
       </c>
       <c r="L44" s="0"/>
-      <c r="M44" s="0" t="b">
-        <v>0</v>
+      <c r="M44" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N44" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="0" t="b">
         <v>1</v>
@@ -3202,6 +3420,9 @@
         <v>1</v>
       </c>
       <c r="Q44" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R44" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3254,19 +3475,24 @@
         <v>10</v>
       </c>
       <c r="L45" s="0"/>
-      <c r="M45" s="0" t="b">
-        <v>0</v>
+      <c r="M45" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N45" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O45" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q45" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R45" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3319,11 +3545,13 @@
         <v>4</v>
       </c>
       <c r="L46" s="0"/>
-      <c r="M46" s="0" t="b">
-        <v>0</v>
+      <c r="M46" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N46" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" s="0" t="b">
         <v>1</v>
@@ -3332,6 +3560,9 @@
         <v>1</v>
       </c>
       <c r="Q46" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R46" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3384,11 +3615,13 @@
         <v>5</v>
       </c>
       <c r="L47" s="0"/>
-      <c r="M47" s="0" t="b">
-        <v>0</v>
+      <c r="M47" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N47" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" s="0" t="b">
         <v>1</v>
@@ -3397,6 +3630,9 @@
         <v>1</v>
       </c>
       <c r="Q47" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R47" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3449,8 +3685,10 @@
         <v>19</v>
       </c>
       <c r="L48" s="0"/>
-      <c r="M48" s="0" t="b">
-        <v>0</v>
+      <c r="M48" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N48" s="0" t="b">
         <v>0</v>
@@ -3459,9 +3697,12 @@
         <v>0</v>
       </c>
       <c r="P48" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R48" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3514,19 +3755,24 @@
         <v>8</v>
       </c>
       <c r="L49" s="0"/>
-      <c r="M49" s="0" t="b">
-        <v>0</v>
+      <c r="M49" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N49" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O49" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q49" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R49" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3579,8 +3825,10 @@
         <v>16</v>
       </c>
       <c r="L50" s="0"/>
-      <c r="M50" s="0" t="b">
-        <v>0</v>
+      <c r="M50" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N50" s="0" t="b">
         <v>0</v>
@@ -3589,9 +3837,12 @@
         <v>0</v>
       </c>
       <c r="P50" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R50" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3644,8 +3895,10 @@
         <v>21</v>
       </c>
       <c r="L51" s="0"/>
-      <c r="M51" s="0" t="b">
-        <v>0</v>
+      <c r="M51" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N51" s="0" t="b">
         <v>0</v>
@@ -3654,9 +3907,12 @@
         <v>0</v>
       </c>
       <c r="P51" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R51" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3709,8 +3965,10 @@
         <v>16</v>
       </c>
       <c r="L52" s="0"/>
-      <c r="M52" s="0" t="b">
-        <v>0</v>
+      <c r="M52" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N52" s="0" t="b">
         <v>0</v>
@@ -3719,9 +3977,12 @@
         <v>0</v>
       </c>
       <c r="P52" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R52" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3774,11 +4035,13 @@
         <v>5</v>
       </c>
       <c r="L53" s="0"/>
-      <c r="M53" s="0" t="b">
-        <v>0</v>
+      <c r="M53" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N53" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" s="0" t="b">
         <v>1</v>
@@ -3787,6 +4050,9 @@
         <v>1</v>
       </c>
       <c r="Q53" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R53" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3839,11 +4105,13 @@
         <v>6</v>
       </c>
       <c r="L54" s="0"/>
-      <c r="M54" s="0" t="b">
-        <v>0</v>
+      <c r="M54" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N54" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" s="0" t="b">
         <v>1</v>
@@ -3852,6 +4120,9 @@
         <v>1</v>
       </c>
       <c r="Q54" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R54" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3904,8 +4175,10 @@
         <v>16</v>
       </c>
       <c r="L55" s="0"/>
-      <c r="M55" s="0" t="b">
-        <v>0</v>
+      <c r="M55" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N55" s="0" t="b">
         <v>0</v>
@@ -3914,9 +4187,12 @@
         <v>0</v>
       </c>
       <c r="P55" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R55" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3969,8 +4245,10 @@
         <v>15</v>
       </c>
       <c r="L56" s="0"/>
-      <c r="M56" s="0" t="b">
-        <v>0</v>
+      <c r="M56" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N56" s="0" t="b">
         <v>0</v>
@@ -3979,9 +4257,12 @@
         <v>0</v>
       </c>
       <c r="P56" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R56" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4034,8 +4315,10 @@
         <v>21</v>
       </c>
       <c r="L57" s="0"/>
-      <c r="M57" s="0" t="b">
-        <v>0</v>
+      <c r="M57" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N57" s="0" t="b">
         <v>0</v>
@@ -4044,9 +4327,12 @@
         <v>0</v>
       </c>
       <c r="P57" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R57" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4099,11 +4385,13 @@
         <v>2</v>
       </c>
       <c r="L58" s="0"/>
-      <c r="M58" s="0" t="b">
-        <v>0</v>
+      <c r="M58" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N58" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" s="0" t="b">
         <v>1</v>
@@ -4112,6 +4400,9 @@
         <v>1</v>
       </c>
       <c r="Q58" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R58" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4164,19 +4455,24 @@
         <v>11</v>
       </c>
       <c r="L59" s="0"/>
-      <c r="M59" s="0" t="b">
-        <v>0</v>
+      <c r="M59" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N59" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O59" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P59" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q59" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R59" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4229,11 +4525,13 @@
         <v>3</v>
       </c>
       <c r="L60" s="0"/>
-      <c r="M60" s="0" t="b">
-        <v>0</v>
+      <c r="M60" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N60" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" s="0" t="b">
         <v>1</v>
@@ -4242,6 +4540,9 @@
         <v>1</v>
       </c>
       <c r="Q60" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R60" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4294,19 +4595,24 @@
         <v>9</v>
       </c>
       <c r="L61" s="0"/>
-      <c r="M61" s="0" t="b">
-        <v>0</v>
+      <c r="M61" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N61" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O61" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P61" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q61" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R61" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4359,19 +4665,24 @@
         <v>10</v>
       </c>
       <c r="L62" s="0"/>
-      <c r="M62" s="0" t="b">
-        <v>0</v>
+      <c r="M62" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N62" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O62" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P62" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q62" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R62" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4424,8 +4735,10 @@
         <v>19</v>
       </c>
       <c r="L63" s="0"/>
-      <c r="M63" s="0" t="b">
-        <v>0</v>
+      <c r="M63" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N63" s="0" t="b">
         <v>0</v>
@@ -4434,9 +4747,12 @@
         <v>0</v>
       </c>
       <c r="P63" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q63" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R63" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4489,11 +4805,13 @@
         <v>5</v>
       </c>
       <c r="L64" s="0"/>
-      <c r="M64" s="0" t="b">
-        <v>0</v>
+      <c r="M64" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N64" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" s="0" t="b">
         <v>1</v>
@@ -4502,6 +4820,9 @@
         <v>1</v>
       </c>
       <c r="Q64" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R64" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4554,19 +4875,24 @@
         <v>9</v>
       </c>
       <c r="L65" s="0"/>
-      <c r="M65" s="0" t="b">
-        <v>0</v>
+      <c r="M65" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N65" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O65" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P65" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q65" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R65" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4619,8 +4945,10 @@
         <v>21</v>
       </c>
       <c r="L66" s="0"/>
-      <c r="M66" s="0" t="b">
-        <v>0</v>
+      <c r="M66" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N66" s="0" t="b">
         <v>0</v>
@@ -4629,9 +4957,12 @@
         <v>0</v>
       </c>
       <c r="P66" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q66" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R66" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4684,8 +5015,10 @@
         <v>16</v>
       </c>
       <c r="L67" s="0"/>
-      <c r="M67" s="0" t="b">
-        <v>0</v>
+      <c r="M67" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N67" s="0" t="b">
         <v>0</v>
@@ -4694,9 +5027,12 @@
         <v>0</v>
       </c>
       <c r="P67" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R67" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4749,19 +5085,24 @@
         <v>10</v>
       </c>
       <c r="L68" s="0"/>
-      <c r="M68" s="0" t="b">
-        <v>0</v>
+      <c r="M68" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N68" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O68" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P68" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q68" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R68" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4814,8 +5155,10 @@
         <v>17</v>
       </c>
       <c r="L69" s="0"/>
-      <c r="M69" s="0" t="b">
-        <v>0</v>
+      <c r="M69" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N69" s="0" t="b">
         <v>0</v>
@@ -4824,9 +5167,12 @@
         <v>0</v>
       </c>
       <c r="P69" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q69" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R69" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4879,11 +5225,13 @@
         <v>5</v>
       </c>
       <c r="L70" s="0"/>
-      <c r="M70" s="0" t="b">
-        <v>0</v>
+      <c r="M70" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N70" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" s="0" t="b">
         <v>1</v>
@@ -4892,6 +5240,9 @@
         <v>1</v>
       </c>
       <c r="Q70" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R70" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4944,11 +5295,13 @@
         <v>2</v>
       </c>
       <c r="L71" s="0"/>
-      <c r="M71" s="0" t="b">
-        <v>0</v>
+      <c r="M71" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N71" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" s="0" t="b">
         <v>1</v>
@@ -4957,6 +5310,9 @@
         <v>1</v>
       </c>
       <c r="Q71" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R71" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5009,8 +5365,10 @@
         <v>17</v>
       </c>
       <c r="L72" s="0"/>
-      <c r="M72" s="0" t="b">
-        <v>0</v>
+      <c r="M72" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N72" s="0" t="b">
         <v>0</v>
@@ -5019,9 +5377,12 @@
         <v>0</v>
       </c>
       <c r="P72" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q72" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R72" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5074,19 +5435,24 @@
         <v>8</v>
       </c>
       <c r="L73" s="0"/>
-      <c r="M73" s="0" t="b">
-        <v>0</v>
+      <c r="M73" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N73" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O73" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P73" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q73" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R73" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5139,19 +5505,24 @@
         <v>13</v>
       </c>
       <c r="L74" s="0"/>
-      <c r="M74" s="0" t="b">
-        <v>0</v>
+      <c r="M74" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N74" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O74" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P74" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q74" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R74" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5204,8 +5575,10 @@
         <v>15</v>
       </c>
       <c r="L75" s="0"/>
-      <c r="M75" s="0" t="b">
-        <v>0</v>
+      <c r="M75" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N75" s="0" t="b">
         <v>0</v>
@@ -5214,9 +5587,12 @@
         <v>0</v>
       </c>
       <c r="P75" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R75" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5269,8 +5645,10 @@
         <v>15</v>
       </c>
       <c r="L76" s="0"/>
-      <c r="M76" s="0" t="b">
-        <v>0</v>
+      <c r="M76" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N76" s="0" t="b">
         <v>0</v>
@@ -5279,9 +5657,12 @@
         <v>0</v>
       </c>
       <c r="P76" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q76" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R76" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5334,11 +5715,13 @@
         <v>6</v>
       </c>
       <c r="L77" s="0"/>
-      <c r="M77" s="0" t="b">
-        <v>0</v>
+      <c r="M77" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N77" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" s="0" t="b">
         <v>1</v>
@@ -5347,6 +5730,9 @@
         <v>1</v>
       </c>
       <c r="Q77" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R77" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5399,11 +5785,13 @@
         <v>5</v>
       </c>
       <c r="L78" s="0"/>
-      <c r="M78" s="0" t="b">
-        <v>0</v>
+      <c r="M78" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N78" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O78" s="0" t="b">
         <v>1</v>
@@ -5412,6 +5800,9 @@
         <v>1</v>
       </c>
       <c r="Q78" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R78" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5464,8 +5855,10 @@
         <v>16</v>
       </c>
       <c r="L79" s="0"/>
-      <c r="M79" s="0" t="b">
-        <v>0</v>
+      <c r="M79" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N79" s="0" t="b">
         <v>0</v>
@@ -5474,9 +5867,12 @@
         <v>0</v>
       </c>
       <c r="P79" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q79" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R79" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5529,8 +5925,10 @@
         <v>19</v>
       </c>
       <c r="L80" s="0"/>
-      <c r="M80" s="0" t="b">
-        <v>0</v>
+      <c r="M80" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N80" s="0" t="b">
         <v>0</v>
@@ -5539,9 +5937,12 @@
         <v>0</v>
       </c>
       <c r="P80" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q80" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R80" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5594,19 +5995,24 @@
         <v>14</v>
       </c>
       <c r="L81" s="0"/>
-      <c r="M81" s="0" t="b">
-        <v>0</v>
+      <c r="M81" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N81" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O81" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P81" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q81" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R81" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5659,19 +6065,24 @@
         <v>11</v>
       </c>
       <c r="L82" s="0"/>
-      <c r="M82" s="0" t="b">
-        <v>0</v>
+      <c r="M82" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N82" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O82" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P82" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q82" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R82" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5724,8 +6135,10 @@
         <v>21</v>
       </c>
       <c r="L83" s="0"/>
-      <c r="M83" s="0" t="b">
-        <v>0</v>
+      <c r="M83" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N83" s="0" t="b">
         <v>0</v>
@@ -5734,9 +6147,12 @@
         <v>0</v>
       </c>
       <c r="P83" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R83" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5789,19 +6205,24 @@
         <v>14</v>
       </c>
       <c r="L84" s="0"/>
-      <c r="M84" s="0" t="b">
-        <v>0</v>
+      <c r="M84" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N84" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O84" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P84" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q84" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R84" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5854,19 +6275,24 @@
         <v>11</v>
       </c>
       <c r="L85" s="0"/>
-      <c r="M85" s="0" t="b">
-        <v>0</v>
+      <c r="M85" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N85" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O85" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P85" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q85" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R85" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5919,19 +6345,24 @@
         <v>9</v>
       </c>
       <c r="L86" s="0"/>
-      <c r="M86" s="0" t="b">
-        <v>0</v>
+      <c r="M86" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N86" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O86" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P86" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q86" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R86" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5984,19 +6415,24 @@
         <v>14</v>
       </c>
       <c r="L87" s="0"/>
-      <c r="M87" s="0" t="b">
-        <v>0</v>
+      <c r="M87" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N87" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O87" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P87" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q87" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R87" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6049,11 +6485,13 @@
         <v>7</v>
       </c>
       <c r="L88" s="0"/>
-      <c r="M88" s="0" t="b">
-        <v>0</v>
+      <c r="M88" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N88" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" s="0" t="b">
         <v>1</v>
@@ -6062,6 +6500,9 @@
         <v>1</v>
       </c>
       <c r="Q88" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R88" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6114,11 +6555,13 @@
         <v>7</v>
       </c>
       <c r="L89" s="0"/>
-      <c r="M89" s="0" t="b">
-        <v>0</v>
+      <c r="M89" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N89" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" s="0" t="b">
         <v>1</v>
@@ -6127,6 +6570,9 @@
         <v>1</v>
       </c>
       <c r="Q89" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R89" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6179,19 +6625,24 @@
         <v>10</v>
       </c>
       <c r="L90" s="0"/>
-      <c r="M90" s="0" t="b">
-        <v>0</v>
+      <c r="M90" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N90" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O90" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P90" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q90" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R90" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6244,8 +6695,10 @@
         <v>16</v>
       </c>
       <c r="L91" s="0"/>
-      <c r="M91" s="0" t="b">
-        <v>0</v>
+      <c r="M91" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N91" s="0" t="b">
         <v>0</v>
@@ -6254,9 +6707,12 @@
         <v>0</v>
       </c>
       <c r="P91" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R91" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6309,8 +6765,10 @@
         <v>18</v>
       </c>
       <c r="L92" s="0"/>
-      <c r="M92" s="0" t="b">
-        <v>0</v>
+      <c r="M92" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N92" s="0" t="b">
         <v>0</v>
@@ -6319,9 +6777,12 @@
         <v>0</v>
       </c>
       <c r="P92" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q92" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R92" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6374,11 +6835,13 @@
         <v>7</v>
       </c>
       <c r="L93" s="0"/>
-      <c r="M93" s="0" t="b">
-        <v>0</v>
+      <c r="M93" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N93" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93" s="0" t="b">
         <v>1</v>
@@ -6387,6 +6850,9 @@
         <v>1</v>
       </c>
       <c r="Q93" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R93" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6439,8 +6905,10 @@
         <v>17</v>
       </c>
       <c r="L94" s="0"/>
-      <c r="M94" s="0" t="b">
-        <v>0</v>
+      <c r="M94" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N94" s="0" t="b">
         <v>0</v>
@@ -6449,9 +6917,12 @@
         <v>0</v>
       </c>
       <c r="P94" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q94" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R94" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6504,19 +6975,24 @@
         <v>10</v>
       </c>
       <c r="L95" s="0"/>
-      <c r="M95" s="0" t="b">
-        <v>0</v>
+      <c r="M95" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N95" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O95" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P95" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q95" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R95" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6569,19 +7045,24 @@
         <v>14</v>
       </c>
       <c r="L96" s="0"/>
-      <c r="M96" s="0" t="b">
-        <v>0</v>
+      <c r="M96" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N96" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O96" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P96" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q96" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R96" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6634,19 +7115,24 @@
         <v>13</v>
       </c>
       <c r="L97" s="0"/>
-      <c r="M97" s="0" t="b">
-        <v>0</v>
+      <c r="M97" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N97" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O97" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P97" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q97" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R97" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6699,19 +7185,24 @@
         <v>13</v>
       </c>
       <c r="L98" s="0"/>
-      <c r="M98" s="0" t="b">
-        <v>0</v>
+      <c r="M98" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N98" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O98" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P98" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q98" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R98" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6764,8 +7255,10 @@
         <v>16</v>
       </c>
       <c r="L99" s="0"/>
-      <c r="M99" s="0" t="b">
-        <v>0</v>
+      <c r="M99" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N99" s="0" t="b">
         <v>0</v>
@@ -6774,9 +7267,12 @@
         <v>0</v>
       </c>
       <c r="P99" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q99" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R99" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6829,8 +7325,10 @@
         <v>20</v>
       </c>
       <c r="L100" s="0"/>
-      <c r="M100" s="0" t="b">
-        <v>0</v>
+      <c r="M100" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N100" s="0" t="b">
         <v>0</v>
@@ -6839,9 +7337,12 @@
         <v>0</v>
       </c>
       <c r="P100" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R100" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6894,19 +7395,24 @@
         <v>11</v>
       </c>
       <c r="L101" s="0"/>
-      <c r="M101" s="0" t="b">
-        <v>0</v>
+      <c r="M101" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N101" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O101" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P101" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q101" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R101" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6959,11 +7465,13 @@
         <v>3</v>
       </c>
       <c r="L102" s="0"/>
-      <c r="M102" s="0" t="b">
-        <v>0</v>
+      <c r="M102" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N102" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O102" s="0" t="b">
         <v>1</v>
@@ -6972,6 +7480,9 @@
         <v>1</v>
       </c>
       <c r="Q102" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R102" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7024,8 +7535,10 @@
         <v>15</v>
       </c>
       <c r="L103" s="0"/>
-      <c r="M103" s="0" t="b">
-        <v>0</v>
+      <c r="M103" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N103" s="0" t="b">
         <v>0</v>
@@ -7034,9 +7547,12 @@
         <v>0</v>
       </c>
       <c r="P103" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q103" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R103" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7089,11 +7605,13 @@
         <v>5</v>
       </c>
       <c r="L104" s="0"/>
-      <c r="M104" s="0" t="b">
-        <v>0</v>
+      <c r="M104" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N104" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O104" s="0" t="b">
         <v>1</v>
@@ -7102,6 +7620,9 @@
         <v>1</v>
       </c>
       <c r="Q104" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R104" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7154,11 +7675,13 @@
         <v>5</v>
       </c>
       <c r="L105" s="0"/>
-      <c r="M105" s="0" t="b">
-        <v>0</v>
+      <c r="M105" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N105" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O105" s="0" t="b">
         <v>1</v>
@@ -7167,6 +7690,9 @@
         <v>1</v>
       </c>
       <c r="Q105" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R105" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7219,8 +7745,10 @@
         <v>15</v>
       </c>
       <c r="L106" s="0"/>
-      <c r="M106" s="0" t="b">
-        <v>0</v>
+      <c r="M106" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N106" s="0" t="b">
         <v>0</v>
@@ -7229,9 +7757,12 @@
         <v>0</v>
       </c>
       <c r="P106" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q106" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R106" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7284,19 +7815,24 @@
         <v>12</v>
       </c>
       <c r="L107" s="0"/>
-      <c r="M107" s="0" t="b">
-        <v>0</v>
+      <c r="M107" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N107" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O107" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P107" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q107" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R107" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7349,19 +7885,24 @@
         <v>8</v>
       </c>
       <c r="L108" s="0"/>
-      <c r="M108" s="0" t="b">
-        <v>0</v>
+      <c r="M108" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N108" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O108" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P108" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q108" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R108" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7414,11 +7955,13 @@
         <v>3</v>
       </c>
       <c r="L109" s="0"/>
-      <c r="M109" s="0" t="b">
-        <v>0</v>
+      <c r="M109" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N109" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O109" s="0" t="b">
         <v>1</v>
@@ -7427,6 +7970,9 @@
         <v>1</v>
       </c>
       <c r="Q109" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R109" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7479,8 +8025,10 @@
         <v>18</v>
       </c>
       <c r="L110" s="0"/>
-      <c r="M110" s="0" t="b">
-        <v>0</v>
+      <c r="M110" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N110" s="0" t="b">
         <v>0</v>
@@ -7489,9 +8037,12 @@
         <v>0</v>
       </c>
       <c r="P110" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R110" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7544,19 +8095,24 @@
         <v>13</v>
       </c>
       <c r="L111" s="0"/>
-      <c r="M111" s="0" t="b">
-        <v>0</v>
+      <c r="M111" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N111" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O111" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P111" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q111" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R111" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7609,8 +8165,10 @@
         <v>21</v>
       </c>
       <c r="L112" s="0"/>
-      <c r="M112" s="0" t="b">
-        <v>0</v>
+      <c r="M112" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N112" s="0" t="b">
         <v>0</v>
@@ -7619,9 +8177,12 @@
         <v>0</v>
       </c>
       <c r="P112" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q112" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R112" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7674,11 +8235,13 @@
         <v>5</v>
       </c>
       <c r="L113" s="0"/>
-      <c r="M113" s="0" t="b">
-        <v>0</v>
+      <c r="M113" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N113" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O113" s="0" t="b">
         <v>1</v>
@@ -7687,6 +8250,9 @@
         <v>1</v>
       </c>
       <c r="Q113" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R113" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7739,8 +8305,10 @@
         <v>18</v>
       </c>
       <c r="L114" s="0"/>
-      <c r="M114" s="0" t="b">
-        <v>0</v>
+      <c r="M114" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N114" s="0" t="b">
         <v>0</v>
@@ -7749,9 +8317,12 @@
         <v>0</v>
       </c>
       <c r="P114" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q114" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R114" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7804,8 +8375,10 @@
         <v>20</v>
       </c>
       <c r="L115" s="0"/>
-      <c r="M115" s="0" t="b">
-        <v>0</v>
+      <c r="M115" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N115" s="0" t="b">
         <v>0</v>
@@ -7814,9 +8387,12 @@
         <v>0</v>
       </c>
       <c r="P115" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q115" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R115" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7869,8 +8445,10 @@
         <v>20</v>
       </c>
       <c r="L116" s="0"/>
-      <c r="M116" s="0" t="b">
-        <v>0</v>
+      <c r="M116" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N116" s="0" t="b">
         <v>0</v>
@@ -7879,9 +8457,12 @@
         <v>0</v>
       </c>
       <c r="P116" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q116" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R116" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7934,11 +8515,13 @@
         <v>7</v>
       </c>
       <c r="L117" s="0"/>
-      <c r="M117" s="0" t="b">
-        <v>0</v>
+      <c r="M117" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N117" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O117" s="0" t="b">
         <v>1</v>
@@ -7947,6 +8530,9 @@
         <v>1</v>
       </c>
       <c r="Q117" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R117" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7999,11 +8585,13 @@
         <v>6</v>
       </c>
       <c r="L118" s="0"/>
-      <c r="M118" s="0" t="b">
-        <v>0</v>
+      <c r="M118" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N118" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O118" s="0" t="b">
         <v>1</v>
@@ -8012,6 +8600,9 @@
         <v>1</v>
       </c>
       <c r="Q118" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R118" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8064,11 +8655,13 @@
         <v>2</v>
       </c>
       <c r="L119" s="0"/>
-      <c r="M119" s="0" t="b">
-        <v>0</v>
+      <c r="M119" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N119" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O119" s="0" t="b">
         <v>1</v>
@@ -8077,6 +8670,9 @@
         <v>1</v>
       </c>
       <c r="Q119" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R119" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8129,8 +8725,10 @@
         <v>18</v>
       </c>
       <c r="L120" s="0"/>
-      <c r="M120" s="0" t="b">
-        <v>0</v>
+      <c r="M120" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N120" s="0" t="b">
         <v>0</v>
@@ -8139,9 +8737,12 @@
         <v>0</v>
       </c>
       <c r="P120" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q120" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R120" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8194,8 +8795,10 @@
         <v>21</v>
       </c>
       <c r="L121" s="0"/>
-      <c r="M121" s="0" t="b">
-        <v>0</v>
+      <c r="M121" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N121" s="0" t="b">
         <v>0</v>
@@ -8204,9 +8807,12 @@
         <v>0</v>
       </c>
       <c r="P121" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q121" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R121" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8259,19 +8865,24 @@
         <v>13</v>
       </c>
       <c r="L122" s="0"/>
-      <c r="M122" s="0" t="b">
-        <v>0</v>
+      <c r="M122" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N122" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O122" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P122" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q122" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R122" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8324,8 +8935,10 @@
         <v>19</v>
       </c>
       <c r="L123" s="0"/>
-      <c r="M123" s="0" t="b">
-        <v>0</v>
+      <c r="M123" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N123" s="0" t="b">
         <v>0</v>
@@ -8334,9 +8947,12 @@
         <v>0</v>
       </c>
       <c r="P123" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q123" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R123" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8389,19 +9005,24 @@
         <v>10</v>
       </c>
       <c r="L124" s="0"/>
-      <c r="M124" s="0" t="b">
-        <v>0</v>
+      <c r="M124" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N124" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O124" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P124" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q124" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R124" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8454,11 +9075,13 @@
         <v>6</v>
       </c>
       <c r="L125" s="0"/>
-      <c r="M125" s="0" t="b">
-        <v>0</v>
+      <c r="M125" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N125" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O125" s="0" t="b">
         <v>1</v>
@@ -8467,6 +9090,9 @@
         <v>1</v>
       </c>
       <c r="Q125" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R125" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8519,11 +9145,13 @@
         <v>6</v>
       </c>
       <c r="L126" s="0"/>
-      <c r="M126" s="0" t="b">
-        <v>0</v>
+      <c r="M126" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N126" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O126" s="0" t="b">
         <v>1</v>
@@ -8532,6 +9160,9 @@
         <v>1</v>
       </c>
       <c r="Q126" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R126" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8584,19 +9215,24 @@
         <v>10</v>
       </c>
       <c r="L127" s="0"/>
-      <c r="M127" s="0" t="b">
-        <v>0</v>
+      <c r="M127" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N127" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O127" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P127" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q127" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R127" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8649,8 +9285,10 @@
         <v>17</v>
       </c>
       <c r="L128" s="0"/>
-      <c r="M128" s="0" t="b">
-        <v>0</v>
+      <c r="M128" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N128" s="0" t="b">
         <v>0</v>
@@ -8659,9 +9297,12 @@
         <v>0</v>
       </c>
       <c r="P128" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q128" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R128" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8714,19 +9355,24 @@
         <v>13</v>
       </c>
       <c r="L129" s="0"/>
-      <c r="M129" s="0" t="b">
-        <v>0</v>
+      <c r="M129" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N129" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O129" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P129" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q129" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R129" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8779,8 +9425,10 @@
         <v>20</v>
       </c>
       <c r="L130" s="0"/>
-      <c r="M130" s="0" t="b">
-        <v>0</v>
+      <c r="M130" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N130" s="0" t="b">
         <v>0</v>
@@ -8789,9 +9437,12 @@
         <v>0</v>
       </c>
       <c r="P130" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q130" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R130" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8844,8 +9495,10 @@
         <v>18</v>
       </c>
       <c r="L131" s="0"/>
-      <c r="M131" s="0" t="b">
-        <v>0</v>
+      <c r="M131" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N131" s="0" t="b">
         <v>0</v>
@@ -8854,9 +9507,12 @@
         <v>0</v>
       </c>
       <c r="P131" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q131" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R131" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8909,8 +9565,10 @@
         <v>17</v>
       </c>
       <c r="L132" s="0"/>
-      <c r="M132" s="0" t="b">
-        <v>0</v>
+      <c r="M132" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N132" s="0" t="b">
         <v>0</v>
@@ -8919,9 +9577,12 @@
         <v>0</v>
       </c>
       <c r="P132" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q132" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R132" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8974,11 +9635,13 @@
         <v>3</v>
       </c>
       <c r="L133" s="0"/>
-      <c r="M133" s="0" t="b">
-        <v>0</v>
+      <c r="M133" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N133" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O133" s="0" t="b">
         <v>1</v>
@@ -8987,6 +9650,9 @@
         <v>1</v>
       </c>
       <c r="Q133" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R133" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9039,19 +9705,24 @@
         <v>10</v>
       </c>
       <c r="L134" s="0"/>
-      <c r="M134" s="0" t="b">
-        <v>0</v>
+      <c r="M134" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N134" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O134" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P134" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q134" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R134" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9104,8 +9775,10 @@
         <v>19</v>
       </c>
       <c r="L135" s="0"/>
-      <c r="M135" s="0" t="b">
-        <v>0</v>
+      <c r="M135" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N135" s="0" t="b">
         <v>0</v>
@@ -9114,9 +9787,12 @@
         <v>0</v>
       </c>
       <c r="P135" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q135" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R135" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9169,19 +9845,24 @@
         <v>13</v>
       </c>
       <c r="L136" s="0"/>
-      <c r="M136" s="0" t="b">
-        <v>0</v>
+      <c r="M136" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N136" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O136" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P136" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q136" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R136" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9234,11 +9915,13 @@
         <v>4</v>
       </c>
       <c r="L137" s="0"/>
-      <c r="M137" s="0" t="b">
-        <v>0</v>
+      <c r="M137" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N137" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O137" s="0" t="b">
         <v>1</v>
@@ -9247,6 +9930,9 @@
         <v>1</v>
       </c>
       <c r="Q137" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R137" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9299,11 +9985,13 @@
         <v>5</v>
       </c>
       <c r="L138" s="0"/>
-      <c r="M138" s="0" t="b">
-        <v>0</v>
+      <c r="M138" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N138" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O138" s="0" t="b">
         <v>1</v>
@@ -9312,6 +10000,9 @@
         <v>1</v>
       </c>
       <c r="Q138" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R138" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9352,11 +10043,16 @@
       <c r="L139" s="0" t="n">
         <v>73</v>
       </c>
-      <c r="M139" s="0"/>
+      <c r="M139" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N139" s="0"/>
       <c r="O139" s="0"/>
       <c r="P139" s="0"/>
       <c r="Q139" s="0"/>
+      <c r="R139" s="0"/>
     </row>
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
@@ -9395,11 +10091,16 @@
       <c r="L140" s="0" t="n">
         <v>73</v>
       </c>
-      <c r="M140" s="0"/>
+      <c r="M140" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N140" s="0"/>
       <c r="O140" s="0"/>
       <c r="P140" s="0"/>
       <c r="Q140" s="0"/>
+      <c r="R140" s="0"/>
     </row>
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
@@ -9438,11 +10139,16 @@
       <c r="L141" s="0" t="n">
         <v>73</v>
       </c>
-      <c r="M141" s="0"/>
+      <c r="M141" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N141" s="0"/>
       <c r="O141" s="0"/>
       <c r="P141" s="0"/>
       <c r="Q141" s="0"/>
+      <c r="R141" s="0"/>
     </row>
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
@@ -9481,11 +10187,16 @@
       <c r="L142" s="0" t="n">
         <v>73</v>
       </c>
-      <c r="M142" s="0"/>
+      <c r="M142" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N142" s="0"/>
       <c r="O142" s="0"/>
       <c r="P142" s="0"/>
       <c r="Q142" s="0"/>
+      <c r="R142" s="0"/>
     </row>
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
@@ -9524,11 +10235,16 @@
       <c r="L143" s="0" t="n">
         <v>73</v>
       </c>
-      <c r="M143" s="0"/>
+      <c r="M143" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N143" s="0"/>
       <c r="O143" s="0"/>
       <c r="P143" s="0"/>
       <c r="Q143" s="0"/>
+      <c r="R143" s="0"/>
     </row>
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
@@ -9579,8 +10295,10 @@
         <v>18</v>
       </c>
       <c r="L144" s="0"/>
-      <c r="M144" s="0" t="b">
-        <v>0</v>
+      <c r="M144" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N144" s="0" t="b">
         <v>0</v>
@@ -9589,9 +10307,12 @@
         <v>0</v>
       </c>
       <c r="P144" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q144" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R144" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9644,11 +10365,13 @@
         <v>7</v>
       </c>
       <c r="L145" s="0"/>
-      <c r="M145" s="0" t="b">
-        <v>0</v>
+      <c r="M145" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N145" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O145" s="0" t="b">
         <v>1</v>
@@ -9657,6 +10380,9 @@
         <v>1</v>
       </c>
       <c r="Q145" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R145" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9697,11 +10423,16 @@
       <c r="L146" s="0" t="n">
         <v>72</v>
       </c>
-      <c r="M146" s="0"/>
+      <c r="M146" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N146" s="0"/>
       <c r="O146" s="0"/>
       <c r="P146" s="0"/>
       <c r="Q146" s="0"/>
+      <c r="R146" s="0"/>
     </row>
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
@@ -9752,8 +10483,10 @@
         <v>21</v>
       </c>
       <c r="L147" s="0"/>
-      <c r="M147" s="0" t="b">
-        <v>0</v>
+      <c r="M147" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N147" s="0" t="b">
         <v>0</v>
@@ -9762,9 +10495,12 @@
         <v>0</v>
       </c>
       <c r="P147" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q147" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R147" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9805,11 +10541,16 @@
       <c r="L148" s="0" t="n">
         <v>71</v>
       </c>
-      <c r="M148" s="0"/>
+      <c r="M148" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N148" s="0"/>
       <c r="O148" s="0"/>
       <c r="P148" s="0"/>
       <c r="Q148" s="0"/>
+      <c r="R148" s="0"/>
     </row>
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
@@ -9860,8 +10601,10 @@
         <v>18</v>
       </c>
       <c r="L149" s="0"/>
-      <c r="M149" s="0" t="b">
-        <v>0</v>
+      <c r="M149" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N149" s="0" t="b">
         <v>0</v>
@@ -9870,9 +10613,12 @@
         <v>0</v>
       </c>
       <c r="P149" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q149" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R149" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9925,19 +10671,24 @@
         <v>11</v>
       </c>
       <c r="L150" s="0"/>
-      <c r="M150" s="0" t="b">
-        <v>0</v>
+      <c r="M150" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N150" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O150" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P150" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q150" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R150" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9990,11 +10741,13 @@
         <v>6</v>
       </c>
       <c r="L151" s="0"/>
-      <c r="M151" s="0" t="b">
-        <v>0</v>
+      <c r="M151" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N151" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O151" s="0" t="b">
         <v>1</v>
@@ -10003,6 +10756,9 @@
         <v>1</v>
       </c>
       <c r="Q151" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R151" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10055,19 +10811,24 @@
         <v>10</v>
       </c>
       <c r="L152" s="0"/>
-      <c r="M152" s="0" t="b">
-        <v>0</v>
+      <c r="M152" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N152" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O152" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P152" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q152" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R152" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10120,11 +10881,13 @@
         <v>6</v>
       </c>
       <c r="L153" s="0"/>
-      <c r="M153" s="0" t="b">
-        <v>0</v>
+      <c r="M153" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N153" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O153" s="0" t="b">
         <v>1</v>
@@ -10133,6 +10896,9 @@
         <v>1</v>
       </c>
       <c r="Q153" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R153" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10173,11 +10939,16 @@
       <c r="L154" s="0" t="n">
         <v>69</v>
       </c>
-      <c r="M154" s="0"/>
+      <c r="M154" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N154" s="0"/>
       <c r="O154" s="0"/>
       <c r="P154" s="0"/>
       <c r="Q154" s="0"/>
+      <c r="R154" s="0"/>
     </row>
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
@@ -10228,11 +10999,13 @@
         <v>5</v>
       </c>
       <c r="L155" s="0"/>
-      <c r="M155" s="0" t="b">
-        <v>0</v>
+      <c r="M155" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N155" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O155" s="0" t="b">
         <v>1</v>
@@ -10241,6 +11014,9 @@
         <v>1</v>
       </c>
       <c r="Q155" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R155" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10281,11 +11057,16 @@
       <c r="L156" s="0" t="n">
         <v>68</v>
       </c>
-      <c r="M156" s="0"/>
+      <c r="M156" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N156" s="0"/>
       <c r="O156" s="0"/>
       <c r="P156" s="0"/>
       <c r="Q156" s="0"/>
+      <c r="R156" s="0"/>
     </row>
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
@@ -10336,8 +11117,10 @@
         <v>18</v>
       </c>
       <c r="L157" s="0"/>
-      <c r="M157" s="0" t="b">
-        <v>0</v>
+      <c r="M157" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N157" s="0" t="b">
         <v>0</v>
@@ -10346,9 +11129,12 @@
         <v>0</v>
       </c>
       <c r="P157" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q157" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R157" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10401,11 +11187,13 @@
         <v>3</v>
       </c>
       <c r="L158" s="0"/>
-      <c r="M158" s="0" t="b">
-        <v>0</v>
+      <c r="M158" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N158" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O158" s="0" t="b">
         <v>1</v>
@@ -10414,6 +11202,9 @@
         <v>1</v>
       </c>
       <c r="Q158" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R158" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10454,11 +11245,16 @@
       <c r="L159" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="M159" s="0"/>
+      <c r="M159" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N159" s="0"/>
       <c r="O159" s="0"/>
       <c r="P159" s="0"/>
       <c r="Q159" s="0"/>
+      <c r="R159" s="0"/>
     </row>
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
@@ -10509,11 +11305,13 @@
         <v>4</v>
       </c>
       <c r="L160" s="0"/>
-      <c r="M160" s="0" t="b">
-        <v>0</v>
+      <c r="M160" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N160" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O160" s="0" t="b">
         <v>1</v>
@@ -10522,6 +11320,9 @@
         <v>1</v>
       </c>
       <c r="Q160" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R160" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10574,11 +11375,13 @@
         <v>7</v>
       </c>
       <c r="L161" s="0"/>
-      <c r="M161" s="0" t="b">
-        <v>0</v>
+      <c r="M161" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N161" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O161" s="0" t="b">
         <v>1</v>
@@ -10587,6 +11390,9 @@
         <v>1</v>
       </c>
       <c r="Q161" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R161" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10627,11 +11433,16 @@
       <c r="L162" s="0" t="n">
         <v>62</v>
       </c>
-      <c r="M162" s="0"/>
+      <c r="M162" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N162" s="0"/>
       <c r="O162" s="0"/>
       <c r="P162" s="0"/>
       <c r="Q162" s="0"/>
+      <c r="R162" s="0"/>
     </row>
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
@@ -10670,11 +11481,16 @@
       <c r="L163" s="0" t="n">
         <v>62</v>
       </c>
-      <c r="M163" s="0"/>
+      <c r="M163" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N163" s="0"/>
       <c r="O163" s="0"/>
       <c r="P163" s="0"/>
       <c r="Q163" s="0"/>
+      <c r="R163" s="0"/>
     </row>
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
@@ -10713,11 +11529,16 @@
       <c r="L164" s="0" t="n">
         <v>62</v>
       </c>
-      <c r="M164" s="0"/>
+      <c r="M164" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N164" s="0"/>
       <c r="O164" s="0"/>
       <c r="P164" s="0"/>
       <c r="Q164" s="0"/>
+      <c r="R164" s="0"/>
     </row>
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
@@ -10756,11 +11577,16 @@
       <c r="L165" s="0" t="n">
         <v>61</v>
       </c>
-      <c r="M165" s="0"/>
+      <c r="M165" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N165" s="0"/>
       <c r="O165" s="0"/>
       <c r="P165" s="0"/>
       <c r="Q165" s="0"/>
+      <c r="R165" s="0"/>
     </row>
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
@@ -10799,11 +11625,16 @@
       <c r="L166" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="M166" s="0"/>
+      <c r="M166" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N166" s="0"/>
       <c r="O166" s="0"/>
       <c r="P166" s="0"/>
       <c r="Q166" s="0"/>
+      <c r="R166" s="0"/>
     </row>
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
@@ -10842,11 +11673,16 @@
       <c r="L167" s="0" t="n">
         <v>59</v>
       </c>
-      <c r="M167" s="0"/>
+      <c r="M167" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N167" s="0"/>
       <c r="O167" s="0"/>
       <c r="P167" s="0"/>
       <c r="Q167" s="0"/>
+      <c r="R167" s="0"/>
     </row>
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
@@ -10885,11 +11721,16 @@
       <c r="L168" s="0" t="n">
         <v>59</v>
       </c>
-      <c r="M168" s="0"/>
+      <c r="M168" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N168" s="0"/>
       <c r="O168" s="0"/>
       <c r="P168" s="0"/>
       <c r="Q168" s="0"/>
+      <c r="R168" s="0"/>
     </row>
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
@@ -10928,11 +11769,16 @@
       <c r="L169" s="0" t="n">
         <v>59</v>
       </c>
-      <c r="M169" s="0"/>
+      <c r="M169" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N169" s="0"/>
       <c r="O169" s="0"/>
       <c r="P169" s="0"/>
       <c r="Q169" s="0"/>
+      <c r="R169" s="0"/>
     </row>
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
@@ -10971,11 +11817,16 @@
       <c r="L170" s="0" t="n">
         <v>57</v>
       </c>
-      <c r="M170" s="0"/>
+      <c r="M170" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N170" s="0"/>
       <c r="O170" s="0"/>
       <c r="P170" s="0"/>
       <c r="Q170" s="0"/>
+      <c r="R170" s="0"/>
     </row>
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
@@ -11014,11 +11865,16 @@
       <c r="L171" s="0" t="n">
         <v>56</v>
       </c>
-      <c r="M171" s="0"/>
+      <c r="M171" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N171" s="0"/>
       <c r="O171" s="0"/>
       <c r="P171" s="0"/>
       <c r="Q171" s="0"/>
+      <c r="R171" s="0"/>
     </row>
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
@@ -11057,11 +11913,16 @@
       <c r="L172" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="M172" s="0"/>
+      <c r="M172" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N172" s="0"/>
       <c r="O172" s="0"/>
       <c r="P172" s="0"/>
       <c r="Q172" s="0"/>
+      <c r="R172" s="0"/>
     </row>
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
@@ -11100,11 +11961,16 @@
       <c r="L173" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="M173" s="0"/>
+      <c r="M173" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N173" s="0"/>
       <c r="O173" s="0"/>
       <c r="P173" s="0"/>
       <c r="Q173" s="0"/>
+      <c r="R173" s="0"/>
     </row>
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
@@ -11143,11 +12009,16 @@
       <c r="L174" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="M174" s="0"/>
+      <c r="M174" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N174" s="0"/>
       <c r="O174" s="0"/>
       <c r="P174" s="0"/>
       <c r="Q174" s="0"/>
+      <c r="R174" s="0"/>
     </row>
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
@@ -11186,11 +12057,16 @@
       <c r="L175" s="0" t="n">
         <v>54</v>
       </c>
-      <c r="M175" s="0"/>
+      <c r="M175" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N175" s="0"/>
       <c r="O175" s="0"/>
       <c r="P175" s="0"/>
       <c r="Q175" s="0"/>
+      <c r="R175" s="0"/>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
@@ -11229,11 +12105,16 @@
       <c r="L176" s="0" t="n">
         <v>54</v>
       </c>
-      <c r="M176" s="0"/>
+      <c r="M176" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N176" s="0"/>
       <c r="O176" s="0"/>
       <c r="P176" s="0"/>
       <c r="Q176" s="0"/>
+      <c r="R176" s="0"/>
     </row>
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
@@ -11272,11 +12153,16 @@
       <c r="L177" s="0" t="n">
         <v>53</v>
       </c>
-      <c r="M177" s="0"/>
+      <c r="M177" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N177" s="0"/>
       <c r="O177" s="0"/>
       <c r="P177" s="0"/>
       <c r="Q177" s="0"/>
+      <c r="R177" s="0"/>
     </row>
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
@@ -11315,11 +12201,16 @@
       <c r="L178" s="0" t="n">
         <v>53</v>
       </c>
-      <c r="M178" s="0"/>
+      <c r="M178" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N178" s="0"/>
       <c r="O178" s="0"/>
       <c r="P178" s="0"/>
       <c r="Q178" s="0"/>
+      <c r="R178" s="0"/>
     </row>
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
@@ -11358,11 +12249,16 @@
       <c r="L179" s="0" t="n">
         <v>52</v>
       </c>
-      <c r="M179" s="0"/>
+      <c r="M179" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N179" s="0"/>
       <c r="O179" s="0"/>
       <c r="P179" s="0"/>
       <c r="Q179" s="0"/>
+      <c r="R179" s="0"/>
     </row>
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
@@ -11401,11 +12297,16 @@
       <c r="L180" s="0" t="n">
         <v>52</v>
       </c>
-      <c r="M180" s="0"/>
+      <c r="M180" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N180" s="0"/>
       <c r="O180" s="0"/>
       <c r="P180" s="0"/>
       <c r="Q180" s="0"/>
+      <c r="R180" s="0"/>
     </row>
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
@@ -11444,11 +12345,16 @@
       <c r="L181" s="0" t="n">
         <v>51</v>
       </c>
-      <c r="M181" s="0"/>
+      <c r="M181" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N181" s="0"/>
       <c r="O181" s="0"/>
       <c r="P181" s="0"/>
       <c r="Q181" s="0"/>
+      <c r="R181" s="0"/>
     </row>
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
@@ -11487,11 +12393,16 @@
       <c r="L182" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="M182" s="0"/>
+      <c r="M182" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N182" s="0"/>
       <c r="O182" s="0"/>
       <c r="P182" s="0"/>
       <c r="Q182" s="0"/>
+      <c r="R182" s="0"/>
     </row>
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
@@ -11530,11 +12441,16 @@
       <c r="L183" s="0" t="n">
         <v>49</v>
       </c>
-      <c r="M183" s="0"/>
+      <c r="M183" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N183" s="0"/>
       <c r="O183" s="0"/>
       <c r="P183" s="0"/>
       <c r="Q183" s="0"/>
+      <c r="R183" s="0"/>
     </row>
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
@@ -11573,11 +12489,16 @@
       <c r="L184" s="0" t="n">
         <v>48</v>
       </c>
-      <c r="M184" s="0"/>
+      <c r="M184" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N184" s="0"/>
       <c r="O184" s="0"/>
       <c r="P184" s="0"/>
       <c r="Q184" s="0"/>
+      <c r="R184" s="0"/>
     </row>
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
@@ -11616,11 +12537,16 @@
       <c r="L185" s="0" t="n">
         <v>47</v>
       </c>
-      <c r="M185" s="0"/>
+      <c r="M185" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N185" s="0"/>
       <c r="O185" s="0"/>
       <c r="P185" s="0"/>
       <c r="Q185" s="0"/>
+      <c r="R185" s="0"/>
     </row>
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
@@ -11659,11 +12585,16 @@
       <c r="L186" s="0" t="n">
         <v>47</v>
       </c>
-      <c r="M186" s="0"/>
+      <c r="M186" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N186" s="0"/>
       <c r="O186" s="0"/>
       <c r="P186" s="0"/>
       <c r="Q186" s="0"/>
+      <c r="R186" s="0"/>
     </row>
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
@@ -11702,11 +12633,16 @@
       <c r="L187" s="0" t="n">
         <v>46</v>
       </c>
-      <c r="M187" s="0"/>
+      <c r="M187" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N187" s="0"/>
       <c r="O187" s="0"/>
       <c r="P187" s="0"/>
       <c r="Q187" s="0"/>
+      <c r="R187" s="0"/>
     </row>
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
@@ -11745,11 +12681,16 @@
       <c r="L188" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="M188" s="0"/>
+      <c r="M188" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N188" s="0"/>
       <c r="O188" s="0"/>
       <c r="P188" s="0"/>
       <c r="Q188" s="0"/>
+      <c r="R188" s="0"/>
     </row>
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
@@ -11788,11 +12729,16 @@
       <c r="L189" s="0" t="n">
         <v>44</v>
       </c>
-      <c r="M189" s="0"/>
+      <c r="M189" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N189" s="0"/>
       <c r="O189" s="0"/>
       <c r="P189" s="0"/>
       <c r="Q189" s="0"/>
+      <c r="R189" s="0"/>
     </row>
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
@@ -11831,11 +12777,16 @@
       <c r="L190" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="M190" s="0"/>
+      <c r="M190" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N190" s="0"/>
       <c r="O190" s="0"/>
       <c r="P190" s="0"/>
       <c r="Q190" s="0"/>
+      <c r="R190" s="0"/>
     </row>
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
@@ -11874,11 +12825,16 @@
       <c r="L191" s="0" t="n">
         <v>39</v>
       </c>
-      <c r="M191" s="0"/>
+      <c r="M191" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N191" s="0"/>
       <c r="O191" s="0"/>
       <c r="P191" s="0"/>
       <c r="Q191" s="0"/>
+      <c r="R191" s="0"/>
     </row>
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
@@ -11917,11 +12873,16 @@
       <c r="L192" s="0" t="n">
         <v>37</v>
       </c>
-      <c r="M192" s="0"/>
+      <c r="M192" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N192" s="0"/>
       <c r="O192" s="0"/>
       <c r="P192" s="0"/>
       <c r="Q192" s="0"/>
+      <c r="R192" s="0"/>
     </row>
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
@@ -11960,11 +12921,16 @@
       <c r="L193" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="M193" s="0"/>
+      <c r="M193" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N193" s="0"/>
       <c r="O193" s="0"/>
       <c r="P193" s="0"/>
       <c r="Q193" s="0"/>
+      <c r="R193" s="0"/>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
@@ -12003,11 +12969,16 @@
       <c r="L194" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="M194" s="0"/>
+      <c r="M194" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N194" s="0"/>
       <c r="O194" s="0"/>
       <c r="P194" s="0"/>
       <c r="Q194" s="0"/>
+      <c r="R194" s="0"/>
     </row>
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
@@ -12046,11 +13017,16 @@
       <c r="L195" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="M195" s="0"/>
+      <c r="M195" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N195" s="0"/>
       <c r="O195" s="0"/>
       <c r="P195" s="0"/>
       <c r="Q195" s="0"/>
+      <c r="R195" s="0"/>
     </row>
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
@@ -12089,11 +13065,16 @@
       <c r="L196" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="M196" s="0"/>
+      <c r="M196" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N196" s="0"/>
       <c r="O196" s="0"/>
       <c r="P196" s="0"/>
       <c r="Q196" s="0"/>
+      <c r="R196" s="0"/>
     </row>
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
@@ -12132,11 +13113,16 @@
       <c r="L197" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="M197" s="0"/>
+      <c r="M197" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N197" s="0"/>
       <c r="O197" s="0"/>
       <c r="P197" s="0"/>
       <c r="Q197" s="0"/>
+      <c r="R197" s="0"/>
     </row>
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
@@ -12175,11 +13161,16 @@
       <c r="L198" s="0" t="n">
         <v>32</v>
       </c>
-      <c r="M198" s="0"/>
+      <c r="M198" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N198" s="0"/>
       <c r="O198" s="0"/>
       <c r="P198" s="0"/>
       <c r="Q198" s="0"/>
+      <c r="R198" s="0"/>
     </row>
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
@@ -12218,11 +13209,16 @@
       <c r="L199" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="M199" s="0"/>
+      <c r="M199" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N199" s="0"/>
       <c r="O199" s="0"/>
       <c r="P199" s="0"/>
       <c r="Q199" s="0"/>
+      <c r="R199" s="0"/>
     </row>
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
@@ -12261,11 +13257,16 @@
       <c r="L200" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="M200" s="0"/>
+      <c r="M200" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N200" s="0"/>
       <c r="O200" s="0"/>
       <c r="P200" s="0"/>
       <c r="Q200" s="0"/>
+      <c r="R200" s="0"/>
     </row>
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
@@ -12304,11 +13305,16 @@
       <c r="L201" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="M201" s="0"/>
+      <c r="M201" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N201" s="0"/>
       <c r="O201" s="0"/>
       <c r="P201" s="0"/>
       <c r="Q201" s="0"/>
+      <c r="R201" s="0"/>
     </row>
   </sheetData>
   <sheetCalcPr fullCalcOnLoad="1"/>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -10041,7 +10041,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M195" s="0" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M196" s="0" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M197" s="0" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M198" s="0" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M199" s="0" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M200" s="0" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -10041,7 +10041,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M195" s="0" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M196" s="0" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M197" s="0" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M198" s="0" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M199" s="0" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M200" s="0" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -10041,7 +10041,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M195" s="0" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M196" s="0" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M197" s="0" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M198" s="0" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M199" s="0" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M200" s="0" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -10041,7 +10041,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M195" s="0" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M196" s="0" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M197" s="0" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M198" s="0" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M199" s="0" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M200" s="0" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -10041,7 +10041,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M195" s="0" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M196" s="0" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M197" s="0" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M198" s="0" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M199" s="0" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M200" s="0" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -10041,7 +10041,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M195" s="0" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M196" s="0" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M197" s="0" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M198" s="0" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M199" s="0" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M200" s="0" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -10041,7 +10041,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M195" s="0" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M196" s="0" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M197" s="0" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M198" s="0" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M199" s="0" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M200" s="0" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -10041,7 +10041,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M195" s="0" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M196" s="0" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M197" s="0" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M198" s="0" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M199" s="0" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M200" s="0" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -10041,7 +10041,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M195" s="0" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M196" s="0" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M197" s="0" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M198" s="0" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M199" s="0" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M200" s="0" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -10041,7 +10041,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M195" s="0" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M196" s="0" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M197" s="0" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M198" s="0" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M199" s="0" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M200" s="0" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/dashboard.xlsx
+++ b/data/samples/reports/sample_data_large/dashboard.xlsx
@@ -10041,7 +10041,7 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M195" s="0" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M196" s="0" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M197" s="0" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M198" s="0" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M199" s="0" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M200" s="0" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>
